--- a/business-libraries/test-data/home_school/attribution.xlsx
+++ b/business-libraries/test-data/home_school/attribution.xlsx
@@ -4,8 +4,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="⑤b 归因-计算变量" sheetId="1" r:id="rId1"/>
-    <sheet name="⑤c 归因-分级规则" sheetId="2" r:id="rId2"/>
-    <sheet name="⑥ 归因-红线熔断" sheetId="3" r:id="rId3"/>
+    <sheet name="⑤c 归因项" sheetId="2" r:id="rId2"/>
+    <sheet name="⑤d 证据规则" sheetId="3" r:id="rId3"/>
+    <sheet name="⑤e 分级规则" sheetId="4" r:id="rId4"/>
+    <sheet name="⑥ 归因-红线熔断" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -399,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -426,388 +428,847 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>总负荷指数</v>
+        <v>容器强度</v>
       </c>
       <c r="B2" t="str">
         <v>home_school</v>
       </c>
       <c r="C2" t="str">
-        <v>总分</v>
+        <v>维度[HS_CONTAINER]</v>
       </c>
       <c r="D2" t="str">
-        <v>五题得分总和</v>
+        <v>关系容器承载力，越高表示越脆弱</v>
       </c>
       <c r="E2" t="str">
-        <v>HS_FIVE_Q</v>
+        <v>HS_QUICK</v>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>con1-con3</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>HS_CONTAINER</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>情绪耗竭指数</v>
+        <v>风险总分</v>
       </c>
       <c r="B3" t="str">
         <v>home_school</v>
       </c>
       <c r="C3" t="str">
-        <v>维度[EMOTION]</v>
+        <v>总分</v>
       </c>
       <c r="D3" t="str">
-        <v>情绪状态维度均值</v>
+        <v>双维速查总分</v>
       </c>
       <c r="E3" t="str">
-        <v>HS_FIVE_Q</v>
+        <v>HS_QUICK</v>
       </c>
       <c r="F3" t="str">
-        <v>q1</v>
+        <v/>
       </c>
       <c r="G3" t="str">
-        <v>EMOTION</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>连续低意义感次数</v>
-      </c>
-      <c r="B4" t="str">
-        <v>home_school</v>
-      </c>
-      <c r="C4" t="str">
-        <v>COUNT_CONSECUTIVE(题[q3] &lt;= 2, 4)</v>
-      </c>
-      <c r="D4" t="str">
-        <v>统计最近连续4次评估中意义感知得分&lt;=2的次数</v>
-      </c>
-      <c r="E4" t="str">
-        <v>HS_FIVE_Q</v>
-      </c>
-      <c r="F4" t="str">
-        <v>q3</v>
-      </c>
-      <c r="G4" t="str">
-        <v>MEANING</v>
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S5"/>
+  <dimension ref="A1:J6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>规则编码*</v>
+        <v>归因编码*</v>
       </c>
       <c r="B1" t="str">
+        <v>归因名称*</v>
+      </c>
+      <c r="C1" t="str">
         <v>所属模块*</v>
       </c>
-      <c r="C1" t="str">
-        <v>依据量表编码*</v>
-      </c>
       <c r="D1" t="str">
-        <v>优先级*</v>
+        <v>权重基数*</v>
       </c>
       <c r="E1" t="str">
-        <v>触发条件</v>
+        <v>工具标签*</v>
       </c>
       <c r="F1" t="str">
-        <v>命中等级*</v>
+        <v>归因说明</v>
       </c>
       <c r="G1" t="str">
-        <v>等级中文名*</v>
+        <v>高分表现</v>
       </c>
       <c r="H1" t="str">
-        <v>是否红线熔断*</v>
+        <v>典型诱因</v>
       </c>
       <c r="I1" t="str">
-        <v>主归因*</v>
+        <v>建议动作</v>
       </c>
       <c r="J1" t="str">
-        <v>次归因</v>
-      </c>
-      <c r="K1" t="str">
-        <v>归因理由*</v>
-      </c>
-      <c r="L1" t="str">
-        <v>工具标签*</v>
-      </c>
-      <c r="M1" t="str">
-        <v>结果说明*</v>
-      </c>
-      <c r="N1" t="str">
-        <v>输出动作摘要</v>
-      </c>
-      <c r="O1" t="str">
-        <v>输出工具摘要</v>
-      </c>
-      <c r="P1" t="str">
-        <v>升级条件</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>升级目标</v>
-      </c>
-      <c r="R1" t="str">
-        <v>复评触发条件</v>
-      </c>
-      <c r="S1" t="str">
         <v>手册出处</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>HS-RED-Q1-Q3</v>
+        <v>HS_AT_CONFLICT</v>
       </c>
       <c r="B2" t="str">
+        <v>沟通冲突升级</v>
+      </c>
+      <c r="C2" t="str">
         <v>home_school</v>
       </c>
-      <c r="C2" t="str">
-        <v>HS_FIVE_Q</v>
-      </c>
       <c r="D2" t="str">
-        <v>10</v>
+        <v>1.4</v>
       </c>
       <c r="E2" t="str">
-        <v>题[q1] &gt;= 4 且 题[q3] &gt;= 4</v>
+        <v>home_school,conflict</v>
       </c>
       <c r="F2" t="str">
-        <v>red</v>
+        <v>家长的表达方式已经越过基本尊重的边界，关系进入对抗状态。</v>
       </c>
       <c r="G2" t="str">
-        <v>需立即关注</v>
+        <v>出现威胁、公开抹黑或恶意维权；沟通中反复攻击个人</v>
       </c>
       <c r="H2" t="str">
-        <v>是</v>
+        <v>长期诉求未被回应，或某次事件处理让家长感到不被尊重</v>
       </c>
       <c r="I2" t="str">
-        <v>沟通质量与信任双低</v>
+        <v>不在情绪高点解释责任，先记录家长诉求、事实依据和待核实点，并上报年级组长</v>
       </c>
       <c r="J2" t="str">
-        <v>情绪耗竭</v>
-      </c>
-      <c r="K2" t="str">
-        <v>Q1疲劳&gt;=4分且Q3意义感&lt;=2分，两者同时处于高危水平，教师可能正经历情绪耗竭的核心阶段</v>
-      </c>
-      <c r="L2" t="str">
-        <v>home_school,orange,communication</v>
-      </c>
-      <c r="M2" t="str">
-        <v>沟通质量与信任双低风险同时处于高位，已暂停常规建议并转介。</v>
-      </c>
-      <c r="N2" t="str">
-        <v>建议安排心理专员面谈，暂缓常规班级评估</v>
-      </c>
-      <c r="O2" t="str">
-        <v>家长会沟通模板（应急）、情绪温度计自评</v>
-      </c>
-      <c r="P2" t="str">
-        <v/>
-      </c>
-      <c r="Q2" t="str">
-        <v/>
-      </c>
-      <c r="R2" t="str">
-        <v>下次评估Q1或Q3任一&gt;=3分时触发复评</v>
-      </c>
-      <c r="S2" t="str">
-        <v>PRD 8.2.1</v>
+        <v>家校沟通合作手册v1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>HS-ORANGE</v>
+        <v>HS_AT_CONTAINER</v>
       </c>
       <c r="B3" t="str">
+        <v>关系容器不足</v>
+      </c>
+      <c r="C3" t="str">
         <v>home_school</v>
       </c>
-      <c r="C3" t="str">
-        <v>HS_FIVE_Q</v>
-      </c>
       <c r="D3" t="str">
-        <v>20</v>
+        <v>1.2</v>
       </c>
       <c r="E3" t="str">
-        <v>总分 &gt;= 17</v>
+        <v>home_school,container</v>
       </c>
       <c r="F3" t="str">
-        <v>orange</v>
+        <v>当前关系无法承受一次坦诚而具体的讨论，需要先修复再沟通。</v>
       </c>
       <c r="G3" t="str">
-        <v>需关注</v>
+        <v>一说具体问题就情绪激化；过去无积极沟通经验可调用</v>
       </c>
       <c r="H3" t="str">
-        <v>否</v>
+        <v>缺少日常正向接触，只在出问题时联系</v>
       </c>
       <c r="I3" t="str">
-        <v>家校冲突升级</v>
+        <v>本周主动做一次与问题无关的正向接触，只反馈孩子的一个具体进步</v>
       </c>
       <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v>总分&gt;=17分，教师在多个维度上感受到压力，但未达到红线阈值</v>
-      </c>
-      <c r="L3" t="str">
-        <v>home_school,yellow,visit</v>
-      </c>
-      <c r="M3" t="str">
-        <v>您的整体状态在多个维度上偏高，建议重点关注并选择1-2项工具开始调整。</v>
-      </c>
-      <c r="N3" t="str">
-        <v>建议本月内完成一次深度自评</v>
-      </c>
-      <c r="O3" t="str">
-        <v>家访指引、家校冲突调解框架</v>
-      </c>
-      <c r="P3" t="str">
-        <v>连续3次评估仍为orange</v>
-      </c>
-      <c r="Q3" t="str">
-        <v>升级至red评估流程</v>
-      </c>
-      <c r="R3" t="str">
-        <v/>
-      </c>
-      <c r="S3" t="str">
-        <v>PRD 8.2.1</v>
+        <v>家校沟通合作手册v1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>HS-YELLOW</v>
+        <v>HS_AT_COOP</v>
       </c>
       <c r="B4" t="str">
+        <v>配合度不足</v>
+      </c>
+      <c r="C4" t="str">
         <v>home_school</v>
       </c>
-      <c r="C4" t="str">
-        <v>HS_FIVE_Q</v>
-      </c>
       <c r="D4" t="str">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="E4" t="str">
-        <v>维度[EMOTION] &gt;= 3.5</v>
+        <v>home_school,cooperation</v>
       </c>
       <c r="F4" t="str">
-        <v>yellow</v>
+        <v>家长未参与共同行动，导致校内措施缺少家庭侧的配合。</v>
       </c>
       <c r="G4" t="str">
-        <v>需留意</v>
+        <v>不回消息、约定的事没有落实</v>
       </c>
       <c r="H4" t="str">
-        <v>否</v>
+        <v>家长精力有限或不认同学校的处理方式</v>
       </c>
       <c r="I4" t="str">
-        <v>家长参与度严重不足</v>
+        <v>把请求缩小到一个本周内能完成的具体动作，并明确完成后的反馈方式</v>
       </c>
       <c r="J4" t="str">
-        <v>情绪耗竭</v>
-      </c>
-      <c r="K4" t="str">
-        <v>情绪耗竭维度得分偏高，可能出现轻度职业倦怠的早期信号</v>
-      </c>
-      <c r="L4" t="str">
-        <v>home_school,red,conflict</v>
-      </c>
-      <c r="M4" t="str">
-        <v>您的情绪耗竭维度偏高，建议开始关注自我照顾。</v>
-      </c>
-      <c r="N4" t="str">
-        <v>建议使用自我照顾工具</v>
-      </c>
-      <c r="O4" t="str">
-        <v>家访指引、同伴支持圈</v>
-      </c>
-      <c r="P4" t="str">
-        <v>连续2次评估仍为yellow</v>
-      </c>
-      <c r="Q4" t="str">
-        <v>升级至orange评估流程</v>
-      </c>
-      <c r="R4" t="str">
-        <v/>
-      </c>
-      <c r="S4" t="str">
-        <v>PRD 8.2.1</v>
+        <v>家校沟通合作手册v1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>HS-GREEN</v>
+        <v>HS_AT_ANXIETY</v>
       </c>
       <c r="B5" t="str">
+        <v>家长焦虑过载</v>
+      </c>
+      <c r="C5" t="str">
         <v>home_school</v>
       </c>
-      <c r="C5" t="str">
-        <v>HS_FIVE_Q</v>
-      </c>
       <c r="D5" t="str">
-        <v>100</v>
+        <v>1.1</v>
       </c>
       <c r="E5" t="str">
-        <v/>
+        <v>home_school,anxiety</v>
       </c>
       <c r="F5" t="str">
-        <v>green</v>
+        <v>家长处于高焦虑状态，难以接收和处理复杂信息。</v>
       </c>
       <c r="G5" t="str">
-        <v>状态良好</v>
+        <v>反复确认同一件事；非工作时间频繁发来紧急消息</v>
       </c>
       <c r="H5" t="str">
-        <v>否</v>
+        <v>对孩子状况缺乏可控感，信息来源零散</v>
       </c>
       <c r="I5" t="str">
-        <v>状态稳定</v>
+        <v>固定一个每周反馈时间点，让家长知道什么时候能拿到什么信息，减少不确定感</v>
       </c>
       <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v>当前评估未触发任何风险规则，教师整体状态稳定</v>
-      </c>
-      <c r="L5" t="str">
-        <v>home_school,green</v>
-      </c>
-      <c r="M5" t="str">
-        <v>当前状态整体稳定，保持现有节奏即可。</v>
-      </c>
-      <c r="N5" t="str">
-        <v/>
-      </c>
-      <c r="O5" t="str">
-        <v/>
-      </c>
-      <c r="P5" t="str">
-        <v/>
-      </c>
-      <c r="Q5" t="str">
-        <v/>
-      </c>
-      <c r="R5" t="str">
-        <v/>
-      </c>
-      <c r="S5" t="str">
-        <v>PRD 8.2.1</v>
+        <v>家校沟通合作手册v1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>HS_AT_TRUST</v>
+      </c>
+      <c r="B6" t="str">
+        <v>信任基础薄弱</v>
+      </c>
+      <c r="C6" t="str">
+        <v>home_school</v>
+      </c>
+      <c r="D6" t="str">
+        <v>1.2</v>
+      </c>
+      <c r="E6" t="str">
+        <v>home_school,trust</v>
+      </c>
+      <c r="F6" t="str">
+        <v>家长不相信教师是出于孩子利益在做判断，任何建议都会被质疑。</v>
+      </c>
+      <c r="G6" t="str">
+        <v>对学校既有安排提出较多质疑；不认为教师站在孩子一边</v>
+      </c>
+      <c r="H6" t="str">
+        <v>过往承诺未兑现或信息不透明</v>
+      </c>
+      <c r="I6" t="str">
+        <v>选一件小事，明确承诺并按时兑现，用可验证的行为重建信任</v>
+      </c>
+      <c r="J6" t="str">
+        <v>家校沟通合作手册v1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J6"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G13"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>证据编码*</v>
+      </c>
+      <c r="B1" t="str">
+        <v>归因编码*</v>
+      </c>
+      <c r="C1" t="str">
+        <v>依据量表编码*</v>
+      </c>
+      <c r="D1" t="str">
+        <v>触发条件*</v>
+      </c>
+      <c r="E1" t="str">
+        <v>证据权重*</v>
+      </c>
+      <c r="F1" t="str">
+        <v>证据说明*</v>
+      </c>
+      <c r="G1" t="str">
+        <v>手册出处</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>HS_EV_01</v>
+      </c>
+      <c r="B2" t="str">
+        <v>HS_AT_CONFLICT</v>
+      </c>
+      <c r="C2" t="str">
+        <v>HS_QUICK</v>
+      </c>
+      <c r="D2" t="str">
+        <v>维度[HS_ATTITUDE] &gt;= 4</v>
+      </c>
+      <c r="E2" t="str">
+        <v>3</v>
+      </c>
+      <c r="F2" t="str">
+        <v>沟通态度维度处于高位，已出现越界表达</v>
+      </c>
+      <c r="G2" t="str">
+        <v>家校沟通合作手册v1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>HS_EV_02</v>
+      </c>
+      <c r="B3" t="str">
+        <v>HS_AT_CONFLICT</v>
+      </c>
+      <c r="C3" t="str">
+        <v>HS_QUICK</v>
+      </c>
+      <c r="D3" t="str">
+        <v>题[att3] &gt;= 4</v>
+      </c>
+      <c r="E3" t="str">
+        <v>3</v>
+      </c>
+      <c r="F3" t="str">
+        <v>出现威胁、公开抹黑或恶意维权行为</v>
+      </c>
+      <c r="G3" t="str">
+        <v>家校沟通合作手册v1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>HS_EV_03</v>
+      </c>
+      <c r="B4" t="str">
+        <v>HS_AT_CONFLICT</v>
+      </c>
+      <c r="C4" t="str">
+        <v>HS_QUICK</v>
+      </c>
+      <c r="D4" t="str">
+        <v>维度[HS_ATTITUDE] &gt;= 3</v>
+      </c>
+      <c r="E4" t="str">
+        <v>1</v>
+      </c>
+      <c r="F4" t="str">
+        <v>沟通态度出现值得关注的变化</v>
+      </c>
+      <c r="G4" t="str">
+        <v>家校沟通合作手册v1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>HS_EV_04</v>
+      </c>
+      <c r="B5" t="str">
+        <v>HS_AT_CONTAINER</v>
+      </c>
+      <c r="C5" t="str">
+        <v>HS_QUICK</v>
+      </c>
+      <c r="D5" t="str">
+        <v>维度[HS_CONTAINER] &gt;= 4</v>
+      </c>
+      <c r="E5" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="F5" t="str">
+        <v>关系容器无法承受坦诚讨论</v>
+      </c>
+      <c r="G5" t="str">
+        <v>家校沟通合作手册v1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>HS_EV_05</v>
+      </c>
+      <c r="B6" t="str">
+        <v>HS_AT_CONTAINER</v>
+      </c>
+      <c r="C6" t="str">
+        <v>HS_QUICK</v>
+      </c>
+      <c r="D6" t="str">
+        <v>维度[HS_CONTAINER] &gt;= 3</v>
+      </c>
+      <c r="E6" t="str">
+        <v>1</v>
+      </c>
+      <c r="F6" t="str">
+        <v>关系容器承载力下降</v>
+      </c>
+      <c r="G6" t="str">
+        <v>家校沟通合作手册v1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>HS_EV_06</v>
+      </c>
+      <c r="B7" t="str">
+        <v>HS_AT_COOP</v>
+      </c>
+      <c r="C7" t="str">
+        <v>HS_QUICK</v>
+      </c>
+      <c r="D7" t="str">
+        <v>维度[HS_COOP] &gt;= 4</v>
+      </c>
+      <c r="E7" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="F7" t="str">
+        <v>配合度维度处于高位，共同行动难以落实</v>
+      </c>
+      <c r="G7" t="str">
+        <v>家校沟通合作手册v1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>HS_EV_07</v>
+      </c>
+      <c r="B8" t="str">
+        <v>HS_AT_COOP</v>
+      </c>
+      <c r="C8" t="str">
+        <v>HS_QUICK</v>
+      </c>
+      <c r="D8" t="str">
+        <v>维度[HS_COOP] &gt;= 3</v>
+      </c>
+      <c r="E8" t="str">
+        <v>1</v>
+      </c>
+      <c r="F8" t="str">
+        <v>配合度出现下降</v>
+      </c>
+      <c r="G8" t="str">
+        <v>家校沟通合作手册v1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>HS_EV_21</v>
+      </c>
+      <c r="B9" t="str">
+        <v>HS_AT_ANXIETY</v>
+      </c>
+      <c r="C9" t="str">
+        <v>HS_PARENT_TYPE</v>
+      </c>
+      <c r="D9" t="str">
+        <v>维度[HS_ANXIETY] &gt;= 3.5</v>
+      </c>
+      <c r="E9" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="F9" t="str">
+        <v>家长焦虑水平偏高，难以处理复杂信息</v>
+      </c>
+      <c r="G9" t="str">
+        <v>家校沟通合作手册v1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>HS_EV_22</v>
+      </c>
+      <c r="B10" t="str">
+        <v>HS_AT_ANXIETY</v>
+      </c>
+      <c r="C10" t="str">
+        <v>HS_PARENT_TYPE</v>
+      </c>
+      <c r="D10" t="str">
+        <v>维度[HS_ANXIETY] &gt;= 3</v>
+      </c>
+      <c r="E10" t="str">
+        <v>1</v>
+      </c>
+      <c r="F10" t="str">
+        <v>家长出现焦虑信号</v>
+      </c>
+      <c r="G10" t="str">
+        <v>家校沟通合作手册v1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>HS_EV_23</v>
+      </c>
+      <c r="B11" t="str">
+        <v>HS_AT_TRUST</v>
+      </c>
+      <c r="C11" t="str">
+        <v>HS_PARENT_TYPE</v>
+      </c>
+      <c r="D11" t="str">
+        <v>维度[HS_TRUST] &gt;= 3.5</v>
+      </c>
+      <c r="E11" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="F11" t="str">
+        <v>信任基础薄弱，建议先做信任修复</v>
+      </c>
+      <c r="G11" t="str">
+        <v>家校沟通合作手册v1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>HS_EV_24</v>
+      </c>
+      <c r="B12" t="str">
+        <v>HS_AT_CONFLICT</v>
+      </c>
+      <c r="C12" t="str">
+        <v>HS_PARENT_TYPE</v>
+      </c>
+      <c r="D12" t="str">
+        <v>维度[HS_CONTROL] &gt;= 4</v>
+      </c>
+      <c r="E12" t="str">
+        <v>2</v>
+      </c>
+      <c r="F12" t="str">
+        <v>控制倾向强且质疑较多，存在冲突升级风险</v>
+      </c>
+      <c r="G12" t="str">
+        <v>家校沟通合作手册v1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>HS_EV_25</v>
+      </c>
+      <c r="B13" t="str">
+        <v>HS_AT_TRUST</v>
+      </c>
+      <c r="C13" t="str">
+        <v>HS_PARENT_TYPE</v>
+      </c>
+      <c r="D13" t="str">
+        <v>维度[HS_TRUST] &gt;= 3</v>
+      </c>
+      <c r="E13" t="str">
+        <v>1</v>
+      </c>
+      <c r="F13" t="str">
+        <v>信任基础需要巩固</v>
+      </c>
+      <c r="G13" t="str">
+        <v>家校沟通合作手册v1</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:N6"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>规则编码*</v>
+      </c>
+      <c r="B1" t="str">
+        <v>所属模块*</v>
+      </c>
+      <c r="C1" t="str">
+        <v>依据量表编码</v>
+      </c>
+      <c r="D1" t="str">
+        <v>优先级*</v>
+      </c>
+      <c r="E1" t="str">
+        <v>触发条件</v>
+      </c>
+      <c r="F1" t="str">
+        <v>命中等级*</v>
+      </c>
+      <c r="G1" t="str">
+        <v>等级中文名*</v>
+      </c>
+      <c r="H1" t="str">
+        <v>严重度*</v>
+      </c>
+      <c r="I1" t="str">
+        <v>是否红线熔断*</v>
+      </c>
+      <c r="J1" t="str">
+        <v>结果说明*</v>
+      </c>
+      <c r="K1" t="str">
+        <v>升级条件</v>
+      </c>
+      <c r="L1" t="str">
+        <v>升级目标</v>
+      </c>
+      <c r="M1" t="str">
+        <v>复评触发条件</v>
+      </c>
+      <c r="N1" t="str">
+        <v>手册出处</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>HS_GRADE_E</v>
+      </c>
+      <c r="B2" t="str">
+        <v>home_school</v>
+      </c>
+      <c r="C2" t="str">
+        <v>HS_QUICK</v>
+      </c>
+      <c r="D2" t="str">
+        <v>10</v>
+      </c>
+      <c r="E2" t="str">
+        <v>题[att3] &gt;= 4</v>
+      </c>
+      <c r="F2" t="str">
+        <v>E</v>
+      </c>
+      <c r="G2" t="str">
+        <v>E 级保护通道</v>
+      </c>
+      <c r="H2" t="str">
+        <v>crisis</v>
+      </c>
+      <c r="I2" t="str">
+        <v>是</v>
+      </c>
+      <c r="J2" t="str">
+        <v>出现威胁或恶意维权行为，已转入保护通道，请勿单独沟通。</v>
+      </c>
+      <c r="K2" t="str">
+        <v/>
+      </c>
+      <c r="L2" t="str">
+        <v>年级组长/校方</v>
+      </c>
+      <c r="M2" t="str">
+        <v/>
+      </c>
+      <c r="N2" t="str">
+        <v>家校沟通合作手册v1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>HS_GRADE_D</v>
+      </c>
+      <c r="B3" t="str">
+        <v>home_school</v>
+      </c>
+      <c r="C3" t="str">
+        <v>HS_QUICK</v>
+      </c>
+      <c r="D3" t="str">
+        <v>20</v>
+      </c>
+      <c r="E3" t="str">
+        <v>风险总分 &gt;= 32</v>
+      </c>
+      <c r="F3" t="str">
+        <v>D</v>
+      </c>
+      <c r="G3" t="str">
+        <v>D 级高冲突</v>
+      </c>
+      <c r="H3" t="str">
+        <v>high</v>
+      </c>
+      <c r="I3" t="str">
+        <v>否</v>
+      </c>
+      <c r="J3" t="str">
+        <v>沟通风险较高，建议由年级组长陪同沟通并全程留痕。</v>
+      </c>
+      <c r="K3" t="str">
+        <v>连续两次 D 级</v>
+      </c>
+      <c r="L3" t="str">
+        <v>年级组长</v>
+      </c>
+      <c r="M3" t="str">
+        <v>7天后复评</v>
+      </c>
+      <c r="N3" t="str">
+        <v>家校沟通合作手册v1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>HS_GRADE_C</v>
+      </c>
+      <c r="B4" t="str">
+        <v>home_school</v>
+      </c>
+      <c r="C4" t="str">
+        <v>HS_QUICK</v>
+      </c>
+      <c r="D4" t="str">
+        <v>30</v>
+      </c>
+      <c r="E4" t="str">
+        <v>风险总分 &gt;= 25</v>
+      </c>
+      <c r="F4" t="str">
+        <v>C</v>
+      </c>
+      <c r="G4" t="str">
+        <v>C 级需谨慎</v>
+      </c>
+      <c r="H4" t="str">
+        <v>high</v>
+      </c>
+      <c r="I4" t="str">
+        <v>否</v>
+      </c>
+      <c r="J4" t="str">
+        <v>沟通存在明显阻力，建议先稳住情绪和事实边界，再决定沟通节奏。</v>
+      </c>
+      <c r="K4" t="str">
+        <v>连续两次 C 级</v>
+      </c>
+      <c r="L4" t="str">
+        <v>年级组长</v>
+      </c>
+      <c r="M4" t="str">
+        <v>14天后复评</v>
+      </c>
+      <c r="N4" t="str">
+        <v>家校沟通合作手册v1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>HS_GRADE_B</v>
+      </c>
+      <c r="B5" t="str">
+        <v>home_school</v>
+      </c>
+      <c r="C5" t="str">
+        <v>HS_QUICK</v>
+      </c>
+      <c r="D5" t="str">
+        <v>40</v>
+      </c>
+      <c r="E5" t="str">
+        <v>风险总分 &gt;= 18</v>
+      </c>
+      <c r="F5" t="str">
+        <v>B</v>
+      </c>
+      <c r="G5" t="str">
+        <v>B 级需铺垫</v>
+      </c>
+      <c r="H5" t="str">
+        <v>medium</v>
+      </c>
+      <c r="I5" t="str">
+        <v>否</v>
+      </c>
+      <c r="J5" t="str">
+        <v>沟通前需要做一定铺垫，重点是先修复关系容器。</v>
+      </c>
+      <c r="K5" t="str">
+        <v>复评升级到 C 级或以上</v>
+      </c>
+      <c r="L5" t="str">
+        <v>年级组长</v>
+      </c>
+      <c r="M5" t="str">
+        <v>30天后复评</v>
+      </c>
+      <c r="N5" t="str">
+        <v>家校沟通合作手册v1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>HS_GRADE_A</v>
+      </c>
+      <c r="B6" t="str">
+        <v>home_school</v>
+      </c>
+      <c r="C6" t="str">
+        <v/>
+      </c>
+      <c r="D6" t="str">
+        <v>999</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v>A</v>
+      </c>
+      <c r="G6" t="str">
+        <v>A 级常规沟通</v>
+      </c>
+      <c r="H6" t="str">
+        <v>low</v>
+      </c>
+      <c r="I6" t="str">
+        <v>否</v>
+      </c>
+      <c r="J6" t="str">
+        <v>家校关系状况良好，可按常规节奏沟通。</v>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v/>
+      </c>
+      <c r="M6" t="str">
+        <v/>
+      </c>
+      <c r="N6" t="str">
+        <v>家校沟通合作手册v1</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:N6"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J2"/>
   <sheetData>
     <row r="1">
@@ -847,31 +1308,31 @@
         <v>home_school</v>
       </c>
       <c r="B2" t="str">
-        <v>题[q1] &gt;= 4 且 题[q3] &gt;= 4</v>
+        <v>题[att3] &gt;= 5</v>
       </c>
       <c r="C2" t="str">
-        <v>沟通质量与信任双低，属家校沟通合作模块红线</v>
+        <v>家长出现明确威胁、公开抹黑或恶意维权行为</v>
       </c>
       <c r="D2" t="str">
         <v>module</v>
       </c>
       <c r="E2" t="str">
-        <v>立即阻断常规建议输出，展示求助指引，生成转介工单通知心理专员</v>
+        <v>停止教师单独沟通，转入学校保护通道，全程留痕并由年级组长或校方介入</v>
       </c>
       <c r="F2" t="str">
-        <v>1. 停止当前评估流程 2. 展示危机求助指引 3. 自动创建安全事件 4. 生成转介工单 5. 发送短信通知心理专员</v>
+        <v>停止单独沟通,启用保护通道,全程留痕,通知年级组长,必要时上报校方</v>
       </c>
       <c r="G2" t="str">
-        <v>当事教师完成心理专员面谈，且专员在系统中标记为「已处置」</v>
+        <v>经年级组长评估确认沟通可恢复常规</v>
       </c>
       <c r="H2" t="str">
-        <v>心理专员</v>
+        <v>年级组长</v>
       </c>
       <c r="I2" t="str">
-        <v>[教师姓名]老师在家校沟通合作评估中触发红线：沟通质量与信任双低。请尽快登录系统查看工单。</v>
+        <v>[班级]家校沟通触发 E 级保护通道，请勿让班主任单独沟通。</v>
       </c>
       <c r="J2" t="str">
-        <v>PRD 8.3</v>
+        <v>家校沟通合作手册v1</v>
       </c>
     </row>
   </sheetData>

--- a/business-libraries/test-data/home_school/attribution.xlsx
+++ b/business-libraries/test-data/home_school/attribution.xlsx
@@ -994,7 +994,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1218,51 +1218,183 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>HS_GRADE_A</v>
+        <v>HS_GRADE_TYPE_D</v>
       </c>
       <c r="B6" t="str">
         <v>home_school</v>
       </c>
       <c r="C6" t="str">
-        <v/>
+        <v>HS_PARENT_TYPE</v>
       </c>
       <c r="D6" t="str">
-        <v>999</v>
+        <v>15</v>
       </c>
       <c r="E6" t="str">
-        <v/>
+        <v>均分 &gt;= 4</v>
       </c>
       <c r="F6" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
       <c r="G6" t="str">
-        <v>A 级常规沟通</v>
+        <v>D 级高冲突</v>
       </c>
       <c r="H6" t="str">
-        <v>low</v>
+        <v>high</v>
       </c>
       <c r="I6" t="str">
         <v>否</v>
       </c>
       <c r="J6" t="str">
+        <v>家长分型显示焦虑或控制倾向偏高、信任基础薄弱，建议由年级组长陪同沟通。</v>
+      </c>
+      <c r="K6" t="str">
+        <v>连续两次 D 级</v>
+      </c>
+      <c r="L6" t="str">
+        <v>年级组长</v>
+      </c>
+      <c r="M6" t="str">
+        <v>7天后复评</v>
+      </c>
+      <c r="N6" t="str">
+        <v>家校沟通合作手册v1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>HS_GRADE_TYPE_C</v>
+      </c>
+      <c r="B7" t="str">
+        <v>home_school</v>
+      </c>
+      <c r="C7" t="str">
+        <v>HS_PARENT_TYPE</v>
+      </c>
+      <c r="D7" t="str">
+        <v>25</v>
+      </c>
+      <c r="E7" t="str">
+        <v>均分 &gt;= 3</v>
+      </c>
+      <c r="F7" t="str">
+        <v>C</v>
+      </c>
+      <c r="G7" t="str">
+        <v>C 级需谨慎</v>
+      </c>
+      <c r="H7" t="str">
+        <v>high</v>
+      </c>
+      <c r="I7" t="str">
+        <v>否</v>
+      </c>
+      <c r="J7" t="str">
+        <v>家长分型提示沟通存在明显阻力，先稳住情绪和事实边界再决定节奏。</v>
+      </c>
+      <c r="K7" t="str">
+        <v>连续两次 C 级</v>
+      </c>
+      <c r="L7" t="str">
+        <v>年级组长</v>
+      </c>
+      <c r="M7" t="str">
+        <v>14天后复评</v>
+      </c>
+      <c r="N7" t="str">
+        <v>家校沟通合作手册v1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>HS_GRADE_TYPE_B</v>
+      </c>
+      <c r="B8" t="str">
+        <v>home_school</v>
+      </c>
+      <c r="C8" t="str">
+        <v>HS_PARENT_TYPE</v>
+      </c>
+      <c r="D8" t="str">
+        <v>35</v>
+      </c>
+      <c r="E8" t="str">
+        <v>均分 &gt;= 2</v>
+      </c>
+      <c r="F8" t="str">
+        <v>B</v>
+      </c>
+      <c r="G8" t="str">
+        <v>B 级需铺垫</v>
+      </c>
+      <c r="H8" t="str">
+        <v>medium</v>
+      </c>
+      <c r="I8" t="str">
+        <v>否</v>
+      </c>
+      <c r="J8" t="str">
+        <v>家长分型提示沟通前需要一定铺垫，重点是先修复关系容器。</v>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v/>
+      </c>
+      <c r="M8" t="str">
+        <v/>
+      </c>
+      <c r="N8" t="str">
+        <v>家校沟通合作手册v1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>HS_GRADE_A</v>
+      </c>
+      <c r="B9" t="str">
+        <v>home_school</v>
+      </c>
+      <c r="C9" t="str">
+        <v/>
+      </c>
+      <c r="D9" t="str">
+        <v>999</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v>A</v>
+      </c>
+      <c r="G9" t="str">
+        <v>A 级常规沟通</v>
+      </c>
+      <c r="H9" t="str">
+        <v>low</v>
+      </c>
+      <c r="I9" t="str">
+        <v>否</v>
+      </c>
+      <c r="J9" t="str">
         <v>家校关系状况良好，可按常规节奏沟通。</v>
       </c>
-      <c r="K6" t="str">
+      <c r="K9" t="str">
         <v/>
       </c>
-      <c r="L6" t="str">
+      <c r="L9" t="str">
         <v/>
       </c>
-      <c r="M6" t="str">
+      <c r="M9" t="str">
         <v/>
       </c>
-      <c r="N6" t="str">
+      <c r="N9" t="str">
         <v>家校沟通合作手册v1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N9"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/business-libraries/test-data/home_school/attribution.xlsx
+++ b/business-libraries/test-data/home_school/attribution.xlsx
@@ -434,19 +434,19 @@
         <v>home_school</v>
       </c>
       <c r="C2" t="str">
-        <v>维度[HS_CONTAINER]</v>
+        <v>维度[HS_S1D3]</v>
       </c>
       <c r="D2" t="str">
-        <v>关系容器承载力，越高表示越脆弱</v>
+        <v/>
       </c>
       <c r="E2" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_S1</v>
       </c>
       <c r="F2" t="str">
-        <v>con1-con3</v>
+        <v/>
       </c>
       <c r="G2" t="str">
-        <v>HS_CONTAINER</v>
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -460,10 +460,10 @@
         <v>总分</v>
       </c>
       <c r="D3" t="str">
-        <v>双维速查总分</v>
+        <v/>
       </c>
       <c r="E3" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_S1</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -517,7 +517,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>HS_AT_CONFLICT</v>
+        <v>HS_AT_01</v>
       </c>
       <c r="B2" t="str">
         <v>沟通冲突升级</v>
@@ -549,10 +549,10 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>HS_AT_CONTAINER</v>
+        <v>HS_AT_02</v>
       </c>
       <c r="B3" t="str">
-        <v>关系容器不足</v>
+        <v>角色边界不足</v>
       </c>
       <c r="C3" t="str">
         <v>home_school</v>
@@ -581,10 +581,10 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>HS_AT_COOP</v>
+        <v>HS_AT_03</v>
       </c>
       <c r="B4" t="str">
-        <v>配合度不足</v>
+        <v>参与效能不足</v>
       </c>
       <c r="C4" t="str">
         <v>home_school</v>
@@ -613,7 +613,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>HS_AT_ANXIETY</v>
+        <v>HS_AT_04</v>
       </c>
       <c r="B5" t="str">
         <v>家长焦虑过载</v>
@@ -645,10 +645,10 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>HS_AT_TRUST</v>
+        <v>HS_AT_05</v>
       </c>
       <c r="B6" t="str">
-        <v>信任基础薄弱</v>
+        <v>信任关系薄弱</v>
       </c>
       <c r="C6" t="str">
         <v>home_school</v>
@@ -714,19 +714,19 @@
         <v>HS_EV_01</v>
       </c>
       <c r="B2" t="str">
-        <v>HS_AT_CONFLICT</v>
+        <v>HS_AT_01</v>
       </c>
       <c r="C2" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_S1</v>
       </c>
       <c r="D2" t="str">
-        <v>维度[HS_ATTITUDE] &gt;= 4</v>
+        <v>维度[HS_S1D4] &gt;= 4</v>
       </c>
       <c r="E2" t="str">
         <v>3</v>
       </c>
       <c r="F2" t="str">
-        <v>沟通态度维度处于高位，已出现越界表达</v>
+        <v>沟通质量维度处于高位，已出现越界表达</v>
       </c>
       <c r="G2" t="str">
         <v>家校沟通合作手册v1</v>
@@ -737,13 +737,13 @@
         <v>HS_EV_02</v>
       </c>
       <c r="B3" t="str">
-        <v>HS_AT_CONFLICT</v>
+        <v>HS_AT_01</v>
       </c>
       <c r="C3" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_S1</v>
       </c>
       <c r="D3" t="str">
-        <v>题[att3] &gt;= 4</v>
+        <v>题[q6] &gt;= 4</v>
       </c>
       <c r="E3" t="str">
         <v>3</v>
@@ -760,19 +760,19 @@
         <v>HS_EV_03</v>
       </c>
       <c r="B4" t="str">
-        <v>HS_AT_CONFLICT</v>
+        <v>HS_AT_01</v>
       </c>
       <c r="C4" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_S1</v>
       </c>
       <c r="D4" t="str">
-        <v>维度[HS_ATTITUDE] &gt;= 3</v>
+        <v>维度[HS_S1D4] &gt;= 3</v>
       </c>
       <c r="E4" t="str">
         <v>1</v>
       </c>
       <c r="F4" t="str">
-        <v>沟通态度出现值得关注的变化</v>
+        <v>沟通质量出现值得关注的变化</v>
       </c>
       <c r="G4" t="str">
         <v>家校沟通合作手册v1</v>
@@ -783,19 +783,19 @@
         <v>HS_EV_04</v>
       </c>
       <c r="B5" t="str">
-        <v>HS_AT_CONTAINER</v>
+        <v>HS_AT_02</v>
       </c>
       <c r="C5" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_S1</v>
       </c>
       <c r="D5" t="str">
-        <v>维度[HS_CONTAINER] &gt;= 4</v>
+        <v>维度[HS_S1D3] &gt;= 4</v>
       </c>
       <c r="E5" t="str">
         <v>2.5</v>
       </c>
       <c r="F5" t="str">
-        <v>关系容器无法承受坦诚讨论</v>
+        <v>角色边界无法承受坦诚讨论</v>
       </c>
       <c r="G5" t="str">
         <v>家校沟通合作手册v1</v>
@@ -806,19 +806,19 @@
         <v>HS_EV_05</v>
       </c>
       <c r="B6" t="str">
-        <v>HS_AT_CONTAINER</v>
+        <v>HS_AT_02</v>
       </c>
       <c r="C6" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_S1</v>
       </c>
       <c r="D6" t="str">
-        <v>维度[HS_CONTAINER] &gt;= 3</v>
+        <v>维度[HS_S1D3] &gt;= 3</v>
       </c>
       <c r="E6" t="str">
         <v>1</v>
       </c>
       <c r="F6" t="str">
-        <v>关系容器承载力下降</v>
+        <v>角色边界承载力下降</v>
       </c>
       <c r="G6" t="str">
         <v>家校沟通合作手册v1</v>
@@ -829,19 +829,19 @@
         <v>HS_EV_06</v>
       </c>
       <c r="B7" t="str">
-        <v>HS_AT_COOP</v>
+        <v>HS_AT_03</v>
       </c>
       <c r="C7" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_S1</v>
       </c>
       <c r="D7" t="str">
-        <v>维度[HS_COOP] &gt;= 4</v>
+        <v>维度[HS_S1D1] &gt;= 4</v>
       </c>
       <c r="E7" t="str">
         <v>2.5</v>
       </c>
       <c r="F7" t="str">
-        <v>配合度维度处于高位，共同行动难以落实</v>
+        <v>参与效能维度处于高位，共同行动难以落实</v>
       </c>
       <c r="G7" t="str">
         <v>家校沟通合作手册v1</v>
@@ -852,19 +852,19 @@
         <v>HS_EV_07</v>
       </c>
       <c r="B8" t="str">
-        <v>HS_AT_COOP</v>
+        <v>HS_AT_03</v>
       </c>
       <c r="C8" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_S1</v>
       </c>
       <c r="D8" t="str">
-        <v>维度[HS_COOP] &gt;= 3</v>
+        <v>维度[HS_S1D1] &gt;= 3</v>
       </c>
       <c r="E8" t="str">
         <v>1</v>
       </c>
       <c r="F8" t="str">
-        <v>配合度出现下降</v>
+        <v>参与效能出现下降</v>
       </c>
       <c r="G8" t="str">
         <v>家校沟通合作手册v1</v>
@@ -872,16 +872,16 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>HS_EV_21</v>
+        <v>HS_EV_08</v>
       </c>
       <c r="B9" t="str">
-        <v>HS_AT_ANXIETY</v>
+        <v>HS_AT_04</v>
       </c>
       <c r="C9" t="str">
-        <v>HS_PARENT_TYPE</v>
+        <v>HS_S2</v>
       </c>
       <c r="D9" t="str">
-        <v>维度[HS_ANXIETY] &gt;= 3.5</v>
+        <v>维度[HS_S2D1] &gt;= 3.5</v>
       </c>
       <c r="E9" t="str">
         <v>2.5</v>
@@ -895,16 +895,16 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>HS_EV_22</v>
+        <v>HS_EV_09</v>
       </c>
       <c r="B10" t="str">
-        <v>HS_AT_ANXIETY</v>
+        <v>HS_AT_04</v>
       </c>
       <c r="C10" t="str">
-        <v>HS_PARENT_TYPE</v>
+        <v>HS_S2</v>
       </c>
       <c r="D10" t="str">
-        <v>维度[HS_ANXIETY] &gt;= 3</v>
+        <v>维度[HS_S2D1] &gt;= 3</v>
       </c>
       <c r="E10" t="str">
         <v>1</v>
@@ -918,22 +918,22 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>HS_EV_23</v>
+        <v>HS_EV_10</v>
       </c>
       <c r="B11" t="str">
-        <v>HS_AT_TRUST</v>
+        <v>HS_AT_05</v>
       </c>
       <c r="C11" t="str">
-        <v>HS_PARENT_TYPE</v>
+        <v>HS_S2</v>
       </c>
       <c r="D11" t="str">
-        <v>维度[HS_TRUST] &gt;= 3.5</v>
+        <v>维度[HS_S2D3] &gt;= 3.5</v>
       </c>
       <c r="E11" t="str">
         <v>2.5</v>
       </c>
       <c r="F11" t="str">
-        <v>信任基础薄弱，建议先做信任修复</v>
+        <v>信任关系薄弱，建议先做信任修复</v>
       </c>
       <c r="G11" t="str">
         <v>家校沟通合作手册v1</v>
@@ -941,16 +941,16 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>HS_EV_24</v>
+        <v>HS_EV_11</v>
       </c>
       <c r="B12" t="str">
-        <v>HS_AT_CONFLICT</v>
+        <v>HS_AT_01</v>
       </c>
       <c r="C12" t="str">
-        <v>HS_PARENT_TYPE</v>
+        <v>HS_S2</v>
       </c>
       <c r="D12" t="str">
-        <v>维度[HS_CONTROL] &gt;= 4</v>
+        <v>维度[HS_S2D2] &gt;= 4</v>
       </c>
       <c r="E12" t="str">
         <v>2</v>
@@ -964,22 +964,22 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>HS_EV_25</v>
+        <v>HS_EV_12</v>
       </c>
       <c r="B13" t="str">
-        <v>HS_AT_TRUST</v>
+        <v>HS_AT_05</v>
       </c>
       <c r="C13" t="str">
-        <v>HS_PARENT_TYPE</v>
+        <v>HS_S2</v>
       </c>
       <c r="D13" t="str">
-        <v>维度[HS_TRUST] &gt;= 3</v>
+        <v>维度[HS_S2D3] &gt;= 3</v>
       </c>
       <c r="E13" t="str">
         <v>1</v>
       </c>
       <c r="F13" t="str">
-        <v>信任基础需要巩固</v>
+        <v>信任关系需要巩固</v>
       </c>
       <c r="G13" t="str">
         <v>家校沟通合作手册v1</v>
@@ -994,7 +994,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1042,22 +1042,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>HS_GRADE_E</v>
+        <v>HS_GR_01</v>
       </c>
       <c r="B2" t="str">
         <v>home_school</v>
       </c>
       <c r="C2" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_S1</v>
       </c>
       <c r="D2" t="str">
         <v>10</v>
       </c>
       <c r="E2" t="str">
-        <v>题[att3] &gt;= 4</v>
+        <v>题[q6] &gt;= 4</v>
       </c>
       <c r="F2" t="str">
-        <v>E</v>
+        <v>red</v>
       </c>
       <c r="G2" t="str">
         <v>E 级保护通道</v>
@@ -1086,22 +1086,22 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>HS_GRADE_D</v>
+        <v>HS_GR_02</v>
       </c>
       <c r="B3" t="str">
         <v>home_school</v>
       </c>
       <c r="C3" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_S2</v>
       </c>
       <c r="D3" t="str">
         <v>20</v>
       </c>
       <c r="E3" t="str">
-        <v>风险总分 &gt;= 32</v>
+        <v>均分 &gt;= 4</v>
       </c>
       <c r="F3" t="str">
-        <v>D</v>
+        <v>orange</v>
       </c>
       <c r="G3" t="str">
         <v>D 级高冲突</v>
@@ -1113,7 +1113,7 @@
         <v>否</v>
       </c>
       <c r="J3" t="str">
-        <v>沟通风险较高，建议由年级组长陪同沟通并全程留痕。</v>
+        <v>家长分型显示焦虑或控制倾向偏高、信任关系薄弱，建议由年级组长陪同沟通。</v>
       </c>
       <c r="K3" t="str">
         <v>连续两次 D 级</v>
@@ -1130,34 +1130,34 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>HS_GRADE_C</v>
+        <v>HS_GR_03</v>
       </c>
       <c r="B4" t="str">
         <v>home_school</v>
       </c>
       <c r="C4" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_S2</v>
       </c>
       <c r="D4" t="str">
         <v>30</v>
       </c>
       <c r="E4" t="str">
-        <v>风险总分 &gt;= 25</v>
+        <v>均分 &gt;= 3</v>
       </c>
       <c r="F4" t="str">
-        <v>C</v>
+        <v>yellow</v>
       </c>
       <c r="G4" t="str">
         <v>C 级需谨慎</v>
       </c>
       <c r="H4" t="str">
-        <v>high</v>
+        <v>medium</v>
       </c>
       <c r="I4" t="str">
         <v>否</v>
       </c>
       <c r="J4" t="str">
-        <v>沟通存在明显阻力，建议先稳住情绪和事实边界，再决定沟通节奏。</v>
+        <v>家长分型提示沟通存在明显阻力，先稳住情绪和事实边界再决定节奏。</v>
       </c>
       <c r="K4" t="str">
         <v>连续两次 C 级</v>
@@ -1174,43 +1174,43 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>HS_GRADE_B</v>
+        <v>HS_GR_AUTO_01</v>
       </c>
       <c r="B5" t="str">
         <v>home_school</v>
       </c>
       <c r="C5" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_S1</v>
       </c>
       <c r="D5" t="str">
-        <v>40</v>
+        <v>501</v>
       </c>
       <c r="E5" t="str">
-        <v>风险总分 &gt;= 18</v>
+        <v>均分 &gt;= 4</v>
       </c>
       <c r="F5" t="str">
-        <v>B</v>
+        <v>orange</v>
       </c>
       <c r="G5" t="str">
-        <v>B 级需铺垫</v>
+        <v>D 级高冲突</v>
       </c>
       <c r="H5" t="str">
-        <v>medium</v>
+        <v>high</v>
       </c>
       <c r="I5" t="str">
         <v>否</v>
       </c>
       <c r="J5" t="str">
-        <v>沟通前需要做一定铺垫，重点是先修复关系容器。</v>
+        <v>家长分型显示焦虑或控制倾向偏高、信任关系薄弱，建议由年级组长陪同沟通。</v>
       </c>
       <c r="K5" t="str">
-        <v>复评升级到 C 级或以上</v>
+        <v/>
       </c>
       <c r="L5" t="str">
-        <v>年级组长</v>
+        <v/>
       </c>
       <c r="M5" t="str">
-        <v>30天后复评</v>
+        <v/>
       </c>
       <c r="N5" t="str">
         <v>家校沟通合作手册v1</v>
@@ -1218,43 +1218,43 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>HS_GRADE_TYPE_D</v>
+        <v>HS_GR_AUTO_02</v>
       </c>
       <c r="B6" t="str">
         <v>home_school</v>
       </c>
       <c r="C6" t="str">
-        <v>HS_PARENT_TYPE</v>
+        <v>HS_S1</v>
       </c>
       <c r="D6" t="str">
-        <v>15</v>
+        <v>502</v>
       </c>
       <c r="E6" t="str">
-        <v>均分 &gt;= 4</v>
+        <v>均分 &gt;= 3.5</v>
       </c>
       <c r="F6" t="str">
-        <v>D</v>
+        <v>yellow</v>
       </c>
       <c r="G6" t="str">
-        <v>D 级高冲突</v>
+        <v>C 级需谨慎</v>
       </c>
       <c r="H6" t="str">
-        <v>high</v>
+        <v>medium</v>
       </c>
       <c r="I6" t="str">
         <v>否</v>
       </c>
       <c r="J6" t="str">
-        <v>家长分型显示焦虑或控制倾向偏高、信任基础薄弱，建议由年级组长陪同沟通。</v>
+        <v>家长分型提示沟通存在明显阻力，先稳住情绪和事实边界再决定节奏。</v>
       </c>
       <c r="K6" t="str">
-        <v>连续两次 D 级</v>
+        <v/>
       </c>
       <c r="L6" t="str">
-        <v>年级组长</v>
+        <v/>
       </c>
       <c r="M6" t="str">
-        <v>7天后复评</v>
+        <v/>
       </c>
       <c r="N6" t="str">
         <v>家校沟通合作手册v1</v>
@@ -1262,139 +1262,51 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>HS_GRADE_TYPE_C</v>
+        <v>HS_GR_DEFAULT</v>
       </c>
       <c r="B7" t="str">
         <v>home_school</v>
       </c>
       <c r="C7" t="str">
-        <v>HS_PARENT_TYPE</v>
+        <v/>
       </c>
       <c r="D7" t="str">
-        <v>25</v>
+        <v>999</v>
       </c>
       <c r="E7" t="str">
-        <v>均分 &gt;= 3</v>
+        <v/>
       </c>
       <c r="F7" t="str">
-        <v>C</v>
+        <v>green</v>
       </c>
       <c r="G7" t="str">
-        <v>C 级需谨慎</v>
+        <v>A 级常规沟通</v>
       </c>
       <c r="H7" t="str">
-        <v>high</v>
+        <v>low</v>
       </c>
       <c r="I7" t="str">
         <v>否</v>
       </c>
       <c r="J7" t="str">
-        <v>家长分型提示沟通存在明显阻力，先稳住情绪和事实边界再决定节奏。</v>
+        <v>本次评估未发现需要重点干预的信号</v>
       </c>
       <c r="K7" t="str">
-        <v>连续两次 C 级</v>
+        <v/>
       </c>
       <c r="L7" t="str">
-        <v>年级组长</v>
+        <v/>
       </c>
       <c r="M7" t="str">
-        <v>14天后复评</v>
+        <v/>
       </c>
       <c r="N7" t="str">
-        <v>家校沟通合作手册v1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>HS_GRADE_TYPE_B</v>
-      </c>
-      <c r="B8" t="str">
-        <v>home_school</v>
-      </c>
-      <c r="C8" t="str">
-        <v>HS_PARENT_TYPE</v>
-      </c>
-      <c r="D8" t="str">
-        <v>35</v>
-      </c>
-      <c r="E8" t="str">
-        <v>均分 &gt;= 2</v>
-      </c>
-      <c r="F8" t="str">
-        <v>B</v>
-      </c>
-      <c r="G8" t="str">
-        <v>B 级需铺垫</v>
-      </c>
-      <c r="H8" t="str">
-        <v>medium</v>
-      </c>
-      <c r="I8" t="str">
-        <v>否</v>
-      </c>
-      <c r="J8" t="str">
-        <v>家长分型提示沟通前需要一定铺垫，重点是先修复关系容器。</v>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v/>
-      </c>
-      <c r="M8" t="str">
-        <v/>
-      </c>
-      <c r="N8" t="str">
-        <v>家校沟通合作手册v1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>HS_GRADE_A</v>
-      </c>
-      <c r="B9" t="str">
-        <v>home_school</v>
-      </c>
-      <c r="C9" t="str">
-        <v/>
-      </c>
-      <c r="D9" t="str">
-        <v>999</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v>A</v>
-      </c>
-      <c r="G9" t="str">
-        <v>A 级常规沟通</v>
-      </c>
-      <c r="H9" t="str">
-        <v>low</v>
-      </c>
-      <c r="I9" t="str">
-        <v>否</v>
-      </c>
-      <c r="J9" t="str">
-        <v>家校关系状况良好，可按常规节奏沟通。</v>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v/>
-      </c>
-      <c r="M9" t="str">
-        <v/>
-      </c>
-      <c r="N9" t="str">
         <v>家校沟通合作手册v1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N7"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1440,10 +1352,10 @@
         <v>home_school</v>
       </c>
       <c r="B2" t="str">
-        <v>题[att3] &gt;= 5</v>
+        <v>题[q6] &gt;= 4</v>
       </c>
       <c r="C2" t="str">
-        <v>家长出现明确威胁、公开抹黑或恶意维权行为</v>
+        <v>出现威胁或恶意维权行为，已转入保护通道，请勿单独沟通。</v>
       </c>
       <c r="D2" t="str">
         <v>module</v>
@@ -1452,7 +1364,7 @@
         <v>停止教师单独沟通，转入学校保护通道，全程留痕并由年级组长或校方介入</v>
       </c>
       <c r="F2" t="str">
-        <v>停止单独沟通,启用保护通道,全程留痕,通知年级组长,必要时上报校方</v>
+        <v>停止单独沟通；启用保护通道；全程留痕；通知年级组长；必要时上报校方</v>
       </c>
       <c r="G2" t="str">
         <v>经年级组长评估确认沟通可恢复常规</v>

--- a/business-libraries/test-data/home_school/attribution.xlsx
+++ b/business-libraries/test-data/home_school/attribution.xlsx
@@ -434,19 +434,19 @@
         <v>home_school</v>
       </c>
       <c r="C2" t="str">
-        <v>维度[HS_S1D3]</v>
+        <v>维度[HS_CONTAINER]</v>
       </c>
       <c r="D2" t="str">
-        <v/>
+        <v>关系容器承载力，越高表示越脆弱</v>
       </c>
       <c r="E2" t="str">
-        <v>HS_S1</v>
+        <v>HS_QUICK</v>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>con1-con3</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>HS_CONTAINER</v>
       </c>
     </row>
     <row r="3">
@@ -460,10 +460,10 @@
         <v>总分</v>
       </c>
       <c r="D3" t="str">
-        <v/>
+        <v>双维速查总分</v>
       </c>
       <c r="E3" t="str">
-        <v>HS_S1</v>
+        <v>HS_QUICK</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -517,7 +517,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>HS_AT_01</v>
+        <v>HS_AT_CONFLICT</v>
       </c>
       <c r="B2" t="str">
         <v>沟通冲突升级</v>
@@ -549,10 +549,10 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>HS_AT_02</v>
+        <v>HS_AT_CONTAINER</v>
       </c>
       <c r="B3" t="str">
-        <v>角色边界不足</v>
+        <v>关系容器不足</v>
       </c>
       <c r="C3" t="str">
         <v>home_school</v>
@@ -581,10 +581,10 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>HS_AT_03</v>
+        <v>HS_AT_COOP</v>
       </c>
       <c r="B4" t="str">
-        <v>参与效能不足</v>
+        <v>配合度不足</v>
       </c>
       <c r="C4" t="str">
         <v>home_school</v>
@@ -613,7 +613,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>HS_AT_04</v>
+        <v>HS_AT_ANXIETY</v>
       </c>
       <c r="B5" t="str">
         <v>家长焦虑过载</v>
@@ -645,10 +645,10 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>HS_AT_05</v>
+        <v>HS_AT_TRUST</v>
       </c>
       <c r="B6" t="str">
-        <v>信任关系薄弱</v>
+        <v>信任基础薄弱</v>
       </c>
       <c r="C6" t="str">
         <v>home_school</v>
@@ -714,19 +714,19 @@
         <v>HS_EV_01</v>
       </c>
       <c r="B2" t="str">
-        <v>HS_AT_01</v>
+        <v>HS_AT_CONFLICT</v>
       </c>
       <c r="C2" t="str">
-        <v>HS_S1</v>
+        <v>HS_QUICK</v>
       </c>
       <c r="D2" t="str">
-        <v>维度[HS_S1D4] &gt;= 4</v>
+        <v>维度[HS_ATTITUDE] &gt;= 4</v>
       </c>
       <c r="E2" t="str">
         <v>3</v>
       </c>
       <c r="F2" t="str">
-        <v>沟通质量维度处于高位，已出现越界表达</v>
+        <v>沟通态度维度处于高位，已出现越界表达</v>
       </c>
       <c r="G2" t="str">
         <v>家校沟通合作手册v1</v>
@@ -737,13 +737,13 @@
         <v>HS_EV_02</v>
       </c>
       <c r="B3" t="str">
-        <v>HS_AT_01</v>
+        <v>HS_AT_CONFLICT</v>
       </c>
       <c r="C3" t="str">
-        <v>HS_S1</v>
+        <v>HS_QUICK</v>
       </c>
       <c r="D3" t="str">
-        <v>题[q6] &gt;= 4</v>
+        <v>题[att3] &gt;= 4</v>
       </c>
       <c r="E3" t="str">
         <v>3</v>
@@ -760,19 +760,19 @@
         <v>HS_EV_03</v>
       </c>
       <c r="B4" t="str">
-        <v>HS_AT_01</v>
+        <v>HS_AT_CONFLICT</v>
       </c>
       <c r="C4" t="str">
-        <v>HS_S1</v>
+        <v>HS_QUICK</v>
       </c>
       <c r="D4" t="str">
-        <v>维度[HS_S1D4] &gt;= 3</v>
+        <v>维度[HS_ATTITUDE] &gt;= 3</v>
       </c>
       <c r="E4" t="str">
         <v>1</v>
       </c>
       <c r="F4" t="str">
-        <v>沟通质量出现值得关注的变化</v>
+        <v>沟通态度出现值得关注的变化</v>
       </c>
       <c r="G4" t="str">
         <v>家校沟通合作手册v1</v>
@@ -783,19 +783,19 @@
         <v>HS_EV_04</v>
       </c>
       <c r="B5" t="str">
-        <v>HS_AT_02</v>
+        <v>HS_AT_CONTAINER</v>
       </c>
       <c r="C5" t="str">
-        <v>HS_S1</v>
+        <v>HS_QUICK</v>
       </c>
       <c r="D5" t="str">
-        <v>维度[HS_S1D3] &gt;= 4</v>
+        <v>维度[HS_CONTAINER] &gt;= 4</v>
       </c>
       <c r="E5" t="str">
         <v>2.5</v>
       </c>
       <c r="F5" t="str">
-        <v>角色边界无法承受坦诚讨论</v>
+        <v>关系容器无法承受坦诚讨论</v>
       </c>
       <c r="G5" t="str">
         <v>家校沟通合作手册v1</v>
@@ -806,19 +806,19 @@
         <v>HS_EV_05</v>
       </c>
       <c r="B6" t="str">
-        <v>HS_AT_02</v>
+        <v>HS_AT_CONTAINER</v>
       </c>
       <c r="C6" t="str">
-        <v>HS_S1</v>
+        <v>HS_QUICK</v>
       </c>
       <c r="D6" t="str">
-        <v>维度[HS_S1D3] &gt;= 3</v>
+        <v>维度[HS_CONTAINER] &gt;= 3</v>
       </c>
       <c r="E6" t="str">
         <v>1</v>
       </c>
       <c r="F6" t="str">
-        <v>角色边界承载力下降</v>
+        <v>关系容器承载力下降</v>
       </c>
       <c r="G6" t="str">
         <v>家校沟通合作手册v1</v>
@@ -829,19 +829,19 @@
         <v>HS_EV_06</v>
       </c>
       <c r="B7" t="str">
-        <v>HS_AT_03</v>
+        <v>HS_AT_COOP</v>
       </c>
       <c r="C7" t="str">
-        <v>HS_S1</v>
+        <v>HS_QUICK</v>
       </c>
       <c r="D7" t="str">
-        <v>维度[HS_S1D1] &gt;= 4</v>
+        <v>维度[HS_COOP] &gt;= 4</v>
       </c>
       <c r="E7" t="str">
         <v>2.5</v>
       </c>
       <c r="F7" t="str">
-        <v>参与效能维度处于高位，共同行动难以落实</v>
+        <v>配合度维度处于高位，共同行动难以落实</v>
       </c>
       <c r="G7" t="str">
         <v>家校沟通合作手册v1</v>
@@ -852,19 +852,19 @@
         <v>HS_EV_07</v>
       </c>
       <c r="B8" t="str">
-        <v>HS_AT_03</v>
+        <v>HS_AT_COOP</v>
       </c>
       <c r="C8" t="str">
-        <v>HS_S1</v>
+        <v>HS_QUICK</v>
       </c>
       <c r="D8" t="str">
-        <v>维度[HS_S1D1] &gt;= 3</v>
+        <v>维度[HS_COOP] &gt;= 3</v>
       </c>
       <c r="E8" t="str">
         <v>1</v>
       </c>
       <c r="F8" t="str">
-        <v>参与效能出现下降</v>
+        <v>配合度出现下降</v>
       </c>
       <c r="G8" t="str">
         <v>家校沟通合作手册v1</v>
@@ -872,16 +872,16 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>HS_EV_08</v>
+        <v>HS_EV_21</v>
       </c>
       <c r="B9" t="str">
-        <v>HS_AT_04</v>
+        <v>HS_AT_ANXIETY</v>
       </c>
       <c r="C9" t="str">
-        <v>HS_S2</v>
+        <v>HS_PARENT_TYPE</v>
       </c>
       <c r="D9" t="str">
-        <v>维度[HS_S2D1] &gt;= 3.5</v>
+        <v>维度[HS_ANXIETY] &gt;= 3.5</v>
       </c>
       <c r="E9" t="str">
         <v>2.5</v>
@@ -895,16 +895,16 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>HS_EV_09</v>
+        <v>HS_EV_22</v>
       </c>
       <c r="B10" t="str">
-        <v>HS_AT_04</v>
+        <v>HS_AT_ANXIETY</v>
       </c>
       <c r="C10" t="str">
-        <v>HS_S2</v>
+        <v>HS_PARENT_TYPE</v>
       </c>
       <c r="D10" t="str">
-        <v>维度[HS_S2D1] &gt;= 3</v>
+        <v>维度[HS_ANXIETY] &gt;= 3</v>
       </c>
       <c r="E10" t="str">
         <v>1</v>
@@ -918,22 +918,22 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>HS_EV_10</v>
+        <v>HS_EV_23</v>
       </c>
       <c r="B11" t="str">
-        <v>HS_AT_05</v>
+        <v>HS_AT_TRUST</v>
       </c>
       <c r="C11" t="str">
-        <v>HS_S2</v>
+        <v>HS_PARENT_TYPE</v>
       </c>
       <c r="D11" t="str">
-        <v>维度[HS_S2D3] &gt;= 3.5</v>
+        <v>维度[HS_TRUST] &gt;= 3.5</v>
       </c>
       <c r="E11" t="str">
         <v>2.5</v>
       </c>
       <c r="F11" t="str">
-        <v>信任关系薄弱，建议先做信任修复</v>
+        <v>信任基础薄弱，建议先做信任修复</v>
       </c>
       <c r="G11" t="str">
         <v>家校沟通合作手册v1</v>
@@ -941,16 +941,16 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>HS_EV_11</v>
+        <v>HS_EV_24</v>
       </c>
       <c r="B12" t="str">
-        <v>HS_AT_01</v>
+        <v>HS_AT_CONFLICT</v>
       </c>
       <c r="C12" t="str">
-        <v>HS_S2</v>
+        <v>HS_PARENT_TYPE</v>
       </c>
       <c r="D12" t="str">
-        <v>维度[HS_S2D2] &gt;= 4</v>
+        <v>维度[HS_CONTROL] &gt;= 4</v>
       </c>
       <c r="E12" t="str">
         <v>2</v>
@@ -964,22 +964,22 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>HS_EV_12</v>
+        <v>HS_EV_25</v>
       </c>
       <c r="B13" t="str">
-        <v>HS_AT_05</v>
+        <v>HS_AT_TRUST</v>
       </c>
       <c r="C13" t="str">
-        <v>HS_S2</v>
+        <v>HS_PARENT_TYPE</v>
       </c>
       <c r="D13" t="str">
-        <v>维度[HS_S2D3] &gt;= 3</v>
+        <v>维度[HS_TRUST] &gt;= 3</v>
       </c>
       <c r="E13" t="str">
         <v>1</v>
       </c>
       <c r="F13" t="str">
-        <v>信任关系需要巩固</v>
+        <v>信任基础需要巩固</v>
       </c>
       <c r="G13" t="str">
         <v>家校沟通合作手册v1</v>
@@ -994,7 +994,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:P9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1037,27 +1037,33 @@
         <v>复评触发条件</v>
       </c>
       <c r="N1" t="str">
+        <v>干预工具</v>
+      </c>
+      <c r="O1" t="str">
+        <v>干预动作</v>
+      </c>
+      <c r="P1" t="str">
         <v>手册出处</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>HS_GR_01</v>
+        <v>HS_GRADE_E</v>
       </c>
       <c r="B2" t="str">
         <v>home_school</v>
       </c>
       <c r="C2" t="str">
-        <v>HS_S1</v>
+        <v>HS_QUICK</v>
       </c>
       <c r="D2" t="str">
         <v>10</v>
       </c>
       <c r="E2" t="str">
-        <v>题[q6] &gt;= 4</v>
+        <v>题[att3] &gt;= 4</v>
       </c>
       <c r="F2" t="str">
-        <v>red</v>
+        <v>E</v>
       </c>
       <c r="G2" t="str">
         <v>E 级保护通道</v>
@@ -1081,27 +1087,33 @@
         <v/>
       </c>
       <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
         <v>家校沟通合作手册v1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>HS_GR_02</v>
+        <v>HS_GRADE_D</v>
       </c>
       <c r="B3" t="str">
         <v>home_school</v>
       </c>
       <c r="C3" t="str">
-        <v>HS_S2</v>
+        <v>HS_QUICK</v>
       </c>
       <c r="D3" t="str">
         <v>20</v>
       </c>
       <c r="E3" t="str">
-        <v>均分 &gt;= 4</v>
+        <v>风险总分 &gt;= 32</v>
       </c>
       <c r="F3" t="str">
-        <v>orange</v>
+        <v>D</v>
       </c>
       <c r="G3" t="str">
         <v>D 级高冲突</v>
@@ -1113,7 +1125,7 @@
         <v>否</v>
       </c>
       <c r="J3" t="str">
-        <v>家长分型显示焦虑或控制倾向偏高、信任关系薄弱，建议由年级组长陪同沟通。</v>
+        <v>沟通风险较高，建议由年级组长陪同沟通并全程留痕。</v>
       </c>
       <c r="K3" t="str">
         <v>连续两次 D 级</v>
@@ -1125,39 +1137,45 @@
         <v>7天后复评</v>
       </c>
       <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
         <v>家校沟通合作手册v1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>HS_GR_03</v>
+        <v>HS_GRADE_C</v>
       </c>
       <c r="B4" t="str">
         <v>home_school</v>
       </c>
       <c r="C4" t="str">
-        <v>HS_S2</v>
+        <v>HS_QUICK</v>
       </c>
       <c r="D4" t="str">
         <v>30</v>
       </c>
       <c r="E4" t="str">
-        <v>均分 &gt;= 3</v>
+        <v>风险总分 &gt;= 25</v>
       </c>
       <c r="F4" t="str">
-        <v>yellow</v>
+        <v>C</v>
       </c>
       <c r="G4" t="str">
         <v>C 级需谨慎</v>
       </c>
       <c r="H4" t="str">
-        <v>medium</v>
+        <v>high</v>
       </c>
       <c r="I4" t="str">
         <v>否</v>
       </c>
       <c r="J4" t="str">
-        <v>家长分型提示沟通存在明显阻力，先稳住情绪和事实边界再决定节奏。</v>
+        <v>沟通存在明显阻力，建议先稳住情绪和事实边界，再决定沟通节奏。</v>
       </c>
       <c r="K4" t="str">
         <v>连续两次 C 级</v>
@@ -1169,144 +1187,268 @@
         <v>14天后复评</v>
       </c>
       <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
         <v>家校沟通合作手册v1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>HS_GR_AUTO_01</v>
+        <v>HS_GRADE_B</v>
       </c>
       <c r="B5" t="str">
         <v>home_school</v>
       </c>
       <c r="C5" t="str">
-        <v>HS_S1</v>
+        <v>HS_QUICK</v>
       </c>
       <c r="D5" t="str">
-        <v>501</v>
+        <v>40</v>
       </c>
       <c r="E5" t="str">
-        <v>均分 &gt;= 4</v>
+        <v>风险总分 &gt;= 18</v>
       </c>
       <c r="F5" t="str">
-        <v>orange</v>
+        <v>B</v>
       </c>
       <c r="G5" t="str">
-        <v>D 级高冲突</v>
+        <v>B 级需铺垫</v>
       </c>
       <c r="H5" t="str">
-        <v>high</v>
+        <v>medium</v>
       </c>
       <c r="I5" t="str">
         <v>否</v>
       </c>
       <c r="J5" t="str">
-        <v>家长分型显示焦虑或控制倾向偏高、信任关系薄弱，建议由年级组长陪同沟通。</v>
+        <v>沟通前需要做一定铺垫，重点是先修复关系容器。</v>
       </c>
       <c r="K5" t="str">
-        <v/>
+        <v>复评升级到 C 级或以上</v>
       </c>
       <c r="L5" t="str">
-        <v/>
+        <v>年级组长</v>
       </c>
       <c r="M5" t="str">
-        <v/>
+        <v>30天后复评</v>
       </c>
       <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="P5" t="str">
         <v>家校沟通合作手册v1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>HS_GR_AUTO_02</v>
+        <v>HS_GRADE_TYPE_D</v>
       </c>
       <c r="B6" t="str">
         <v>home_school</v>
       </c>
       <c r="C6" t="str">
-        <v>HS_S1</v>
+        <v>HS_PARENT_TYPE</v>
       </c>
       <c r="D6" t="str">
-        <v>502</v>
+        <v>15</v>
       </c>
       <c r="E6" t="str">
-        <v>均分 &gt;= 3.5</v>
+        <v>均分 &gt;= 4</v>
       </c>
       <c r="F6" t="str">
-        <v>yellow</v>
+        <v>D</v>
       </c>
       <c r="G6" t="str">
-        <v>C 级需谨慎</v>
+        <v>D 级高冲突</v>
       </c>
       <c r="H6" t="str">
-        <v>medium</v>
+        <v>high</v>
       </c>
       <c r="I6" t="str">
         <v>否</v>
       </c>
       <c r="J6" t="str">
-        <v>家长分型提示沟通存在明显阻力，先稳住情绪和事实边界再决定节奏。</v>
+        <v>家长分型显示焦虑或控制倾向偏高、信任基础薄弱，建议由年级组长陪同沟通。</v>
       </c>
       <c r="K6" t="str">
-        <v/>
+        <v>连续两次 D 级</v>
       </c>
       <c r="L6" t="str">
-        <v/>
+        <v>年级组长</v>
       </c>
       <c r="M6" t="str">
-        <v/>
+        <v>7天后复评</v>
       </c>
       <c r="N6" t="str">
+        <v/>
+      </c>
+      <c r="O6" t="str">
+        <v/>
+      </c>
+      <c r="P6" t="str">
         <v>家校沟通合作手册v1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>HS_GR_DEFAULT</v>
+        <v>HS_GRADE_TYPE_C</v>
       </c>
       <c r="B7" t="str">
         <v>home_school</v>
       </c>
       <c r="C7" t="str">
-        <v/>
+        <v>HS_PARENT_TYPE</v>
       </c>
       <c r="D7" t="str">
-        <v>999</v>
+        <v>25</v>
       </c>
       <c r="E7" t="str">
-        <v/>
+        <v>均分 &gt;= 3</v>
       </c>
       <c r="F7" t="str">
-        <v>green</v>
+        <v>C</v>
       </c>
       <c r="G7" t="str">
-        <v>A 级常规沟通</v>
+        <v>C 级需谨慎</v>
       </c>
       <c r="H7" t="str">
-        <v>low</v>
+        <v>high</v>
       </c>
       <c r="I7" t="str">
         <v>否</v>
       </c>
       <c r="J7" t="str">
-        <v>本次评估未发现需要重点干预的信号</v>
+        <v>家长分型提示沟通存在明显阻力，先稳住情绪和事实边界再决定节奏。</v>
       </c>
       <c r="K7" t="str">
-        <v/>
+        <v>连续两次 C 级</v>
       </c>
       <c r="L7" t="str">
-        <v/>
+        <v>年级组长</v>
       </c>
       <c r="M7" t="str">
-        <v/>
+        <v>14天后复评</v>
       </c>
       <c r="N7" t="str">
+        <v/>
+      </c>
+      <c r="O7" t="str">
+        <v/>
+      </c>
+      <c r="P7" t="str">
+        <v>家校沟通合作手册v1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>HS_GRADE_TYPE_B</v>
+      </c>
+      <c r="B8" t="str">
+        <v>home_school</v>
+      </c>
+      <c r="C8" t="str">
+        <v>HS_PARENT_TYPE</v>
+      </c>
+      <c r="D8" t="str">
+        <v>35</v>
+      </c>
+      <c r="E8" t="str">
+        <v>均分 &gt;= 2</v>
+      </c>
+      <c r="F8" t="str">
+        <v>B</v>
+      </c>
+      <c r="G8" t="str">
+        <v>B 级需铺垫</v>
+      </c>
+      <c r="H8" t="str">
+        <v>medium</v>
+      </c>
+      <c r="I8" t="str">
+        <v>否</v>
+      </c>
+      <c r="J8" t="str">
+        <v>家长分型提示沟通前需要一定铺垫，重点是先修复关系容器。</v>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v/>
+      </c>
+      <c r="M8" t="str">
+        <v/>
+      </c>
+      <c r="N8" t="str">
+        <v/>
+      </c>
+      <c r="O8" t="str">
+        <v/>
+      </c>
+      <c r="P8" t="str">
+        <v>家校沟通合作手册v1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>HS_GRADE_A</v>
+      </c>
+      <c r="B9" t="str">
+        <v>home_school</v>
+      </c>
+      <c r="C9" t="str">
+        <v/>
+      </c>
+      <c r="D9" t="str">
+        <v>999</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v>A</v>
+      </c>
+      <c r="G9" t="str">
+        <v>A 级常规沟通</v>
+      </c>
+      <c r="H9" t="str">
+        <v>low</v>
+      </c>
+      <c r="I9" t="str">
+        <v>否</v>
+      </c>
+      <c r="J9" t="str">
+        <v>家校关系状况良好，可按常规节奏沟通。</v>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v/>
+      </c>
+      <c r="M9" t="str">
+        <v/>
+      </c>
+      <c r="N9" t="str">
+        <v/>
+      </c>
+      <c r="O9" t="str">
+        <v/>
+      </c>
+      <c r="P9" t="str">
         <v>家校沟通合作手册v1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P9"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1352,10 +1494,10 @@
         <v>home_school</v>
       </c>
       <c r="B2" t="str">
-        <v>题[q6] &gt;= 4</v>
+        <v>题[att3] &gt;= 5</v>
       </c>
       <c r="C2" t="str">
-        <v>出现威胁或恶意维权行为，已转入保护通道，请勿单独沟通。</v>
+        <v>家长出现明确威胁、公开抹黑或恶意维权行为</v>
       </c>
       <c r="D2" t="str">
         <v>module</v>
@@ -1364,7 +1506,7 @@
         <v>停止教师单独沟通，转入学校保护通道，全程留痕并由年级组长或校方介入</v>
       </c>
       <c r="F2" t="str">
-        <v>停止单独沟通；启用保护通道；全程留痕；通知年级组长；必要时上报校方</v>
+        <v>停止单独沟通,启用保护通道,全程留痕,通知年级组长,必要时上报校方</v>
       </c>
       <c r="G2" t="str">
         <v>经年级组长评估确认沟通可恢复常规</v>

--- a/business-libraries/test-data/home_school/attribution.xlsx
+++ b/business-libraries/test-data/home_school/attribution.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -428,60 +428,37 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>容器强度</v>
+        <v>沟通健康均分</v>
       </c>
       <c r="B2" t="str">
         <v>home_school</v>
       </c>
       <c r="C2" t="str">
-        <v>维度[HS_CONTAINER]</v>
+        <v>均分</v>
       </c>
       <c r="D2" t="str">
-        <v>关系容器承载力，越高表示越脆弱</v>
+        <v/>
       </c>
       <c r="E2" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_S1</v>
       </c>
       <c r="F2" t="str">
-        <v>con1-con3</v>
+        <v/>
       </c>
       <c r="G2" t="str">
-        <v>HS_CONTAINER</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>风险总分</v>
-      </c>
-      <c r="B3" t="str">
-        <v>home_school</v>
-      </c>
-      <c r="C3" t="str">
-        <v>总分</v>
-      </c>
-      <c r="D3" t="str">
-        <v>双维速查总分</v>
-      </c>
-      <c r="E3" t="str">
-        <v>HS_QUICK</v>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G2"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -517,74 +494,74 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>HS_AT_CONFLICT</v>
+        <v>HS_AT_01</v>
       </c>
       <c r="B2" t="str">
-        <v>沟通冲突升级</v>
+        <v>沟通质量薄弱</v>
       </c>
       <c r="C2" t="str">
         <v>home_school</v>
       </c>
       <c r="D2" t="str">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="E2" t="str">
-        <v>home_school,conflict</v>
+        <v>home_school,communication</v>
       </c>
       <c r="F2" t="str">
-        <v>家长的表达方式已经越过基本尊重的边界，关系进入对抗状态。</v>
+        <v>家校信息通道不畅：传递滞后或失真，重要事项无法及时触达家长，沟通氛围紧张、问题被掩盖。</v>
       </c>
       <c r="G2" t="str">
-        <v>出现威胁、公开抹黑或恶意维权；沟通中反复攻击个人</v>
+        <v>重要信息送达无确认；家长被动等待通知，缺乏主动反馈；双方回避或防御性表达</v>
       </c>
       <c r="H2" t="str">
-        <v>长期诉求未被回应，或某次事件处理让家长感到不被尊重</v>
+        <v>缺少稳定固定的沟通渠道与联系节奏；教师很少主动发起正向沟通，只在出问题时联系</v>
       </c>
       <c r="I2" t="str">
-        <v>不在情绪高点解释责任，先记录家长诉求、事实依据和待核实点，并上报年级组长</v>
+        <v>建立每周固定反馈节奏，重要信息送达需家长确认；先做一次与问题无关的正向接触，再谈需要讨论的问题</v>
       </c>
       <c r="J2" t="str">
-        <v>家校沟通合作手册v1</v>
+        <v>家校沟通与合作test0730-AI入口（评估量表V2.0/归因库/干预方案库/关联关系表）</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>HS_AT_CONTAINER</v>
+        <v>HS_AT_02</v>
       </c>
       <c r="B3" t="str">
-        <v>关系容器不足</v>
+        <v>角色边界问题</v>
       </c>
       <c r="C3" t="str">
         <v>home_school</v>
       </c>
       <c r="D3" t="str">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="E3" t="str">
-        <v>home_school,container</v>
+        <v>home_school,boundary</v>
       </c>
       <c r="F3" t="str">
-        <v>当前关系无法承受一次坦诚而具体的讨论，需要先修复再沟通。</v>
+        <v>家长越界或分工不明：非工作时间频繁打扰、过度介入班级事务、公开渠道发布越界言论，教师边界被持续侵蚀。</v>
       </c>
       <c r="G3" t="str">
-        <v>一说具体问题就情绪激化；过去无积极沟通经验可调用</v>
+        <v>非工作时间频繁联系；替教师做决策或过度参与教学；在家长群等公开空间发布越界言论</v>
       </c>
       <c r="H3" t="str">
-        <v>缺少日常正向接触，只在出问题时联系</v>
+        <v>开学初未约定沟通时段、渠道与响应预期；家校职责分工不清，家长焦虑驱动越界代劳</v>
       </c>
       <c r="I3" t="str">
-        <v>本周主动做一次与问题无关的正向接触，只反馈孩子的一个具体进步</v>
+        <v>与家长明确沟通时段、渠道与响应预期，厘清家校职责分工；越界时温和表达专业主导权，不越界也不让家长越界</v>
       </c>
       <c r="J3" t="str">
-        <v>家校沟通合作手册v1</v>
+        <v>家校沟通与合作test0730-AI入口（评估量表V2.0/归因库/干预方案库/关联关系表）</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>HS_AT_COOP</v>
+        <v>HS_AT_03</v>
       </c>
       <c r="B4" t="str">
-        <v>配合度不足</v>
+        <v>教育一致性冲突</v>
       </c>
       <c r="C4" t="str">
         <v>home_school</v>
@@ -593,91 +570,123 @@
         <v>1</v>
       </c>
       <c r="E4" t="str">
-        <v>home_school,cooperation</v>
+        <v>home_school,consistency</v>
       </c>
       <c r="F4" t="str">
-        <v>家长未参与共同行动，导致校内措施缺少家庭侧的配合。</v>
+        <v>家校理念与规则冲突：要求互相矛盾，孩子在两端被拉扯；家长在孩子面前否定教师，学校安排难以落地。</v>
       </c>
       <c r="G4" t="str">
-        <v>不回消息、约定的事没有落实</v>
+        <v>家长在孩子面前唱反调；对学校既有安排公开质疑；理念分歧导致家庭配合缺位</v>
       </c>
       <c r="H4" t="str">
-        <v>家长精力有限或不认同学校的处理方式</v>
+        <v>开学初未就教育理念、规则与期望对齐；分歧处理不当升级为公开否定</v>
       </c>
       <c r="I4" t="str">
-        <v>把请求缩小到一个本周内能完成的具体动作，并明确完成后的反馈方式</v>
+        <v>出现分歧先私下沟通达成共识，再统一对孩子口径；为家长提供可操作的家庭配合指引，降低执行门槛</v>
       </c>
       <c r="J4" t="str">
-        <v>家校沟通合作手册v1</v>
+        <v>家校沟通与合作test0730-AI入口（评估量表V2.0/归因库/干预方案库/关联关系表）</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>HS_AT_ANXIETY</v>
+        <v>HS_AT_04</v>
       </c>
       <c r="B5" t="str">
-        <v>家长焦虑过载</v>
+        <v>信任关系薄弱</v>
       </c>
       <c r="C5" t="str">
         <v>home_school</v>
       </c>
       <c r="D5" t="str">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="E5" t="str">
-        <v>home_school,anxiety</v>
+        <v>home_school,trust</v>
       </c>
       <c r="F5" t="str">
-        <v>家长处于高焦虑状态，难以接收和处理复杂信息。</v>
+        <v>家长不相信教师出于孩子利益做判断：互相猜疑、任何举措都被解读为不怀好意，约定形同虚设，危机时对立激化。</v>
       </c>
       <c r="G5" t="str">
-        <v>反复确认同一件事；非工作时间频繁发来紧急消息</v>
+        <v>经常私下求证、预设恶意解读动机；家长不履约，约定形同虚设；任何建议都被质疑</v>
       </c>
       <c r="H5" t="str">
-        <v>对孩子状况缺乏可控感，信息来源零散</v>
+        <v>过往承诺未兑现或信息不透明；冲突中双方归因偏差，把对方行为往最坏方向解读</v>
       </c>
       <c r="I5" t="str">
-        <v>固定一个每周反馈时间点，让家长知道什么时候能拿到什么信息，减少不确定感</v>
+        <v>选一件小事明确承诺并按时兑现，用可验证的行为重建信任；重大事项主动告知并说明缘由；冲突时先确认善意动机再处理问题</v>
       </c>
       <c r="J5" t="str">
-        <v>家校沟通合作手册v1</v>
+        <v>家校沟通与合作test0730-AI入口（评估量表V2.0/归因库/干预方案库/关联关系表）</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>HS_AT_TRUST</v>
+        <v>HS_AT_05</v>
       </c>
       <c r="B6" t="str">
-        <v>信任基础薄弱</v>
+        <v>参与效能不足</v>
       </c>
       <c r="C6" t="str">
         <v>home_school</v>
       </c>
       <c r="D6" t="str">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="E6" t="str">
-        <v>home_school,trust</v>
+        <v>home_school,cooperation</v>
       </c>
       <c r="F6" t="str">
-        <v>家长不相信教师是出于孩子利益在做判断，任何建议都会被质疑。</v>
+        <v>家长参与停留在口头：建议停留在纸面，问题反复出现，配合缺乏持续性与闭环，教师单方面费力难见效。</v>
       </c>
       <c r="G6" t="str">
-        <v>对学校既有安排提出较多质疑；不认为教师站在孩子一边</v>
+        <v>口头答应但无行动；孩子问题反复出现；家长参与度低，约定难以落实</v>
       </c>
       <c r="H6" t="str">
-        <v>过往承诺未兑现或信息不透明</v>
+        <v>建议大而泛、无期限无反馈节点；家长精力有限或对处理方式不认同</v>
       </c>
       <c r="I6" t="str">
-        <v>选一件小事，明确承诺并按时兑现，用可验证的行为重建信任</v>
+        <v>把建议拆到一周内能完成的最小动作，明确做什么、什么时候、怎么反馈；对微小进步及时肯定，建立家校配合跟踪闭环</v>
       </c>
       <c r="J6" t="str">
-        <v>家校沟通合作手册v1</v>
+        <v>家校沟通与合作test0730-AI入口（评估量表V2.0/归因库/干预方案库/关联关系表）</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>HS_AT_06</v>
+      </c>
+      <c r="B7" t="str">
+        <v>危机响应风险</v>
+      </c>
+      <c r="C7" t="str">
+        <v>home_school</v>
+      </c>
+      <c r="D7" t="str">
+        <v>1.3</v>
+      </c>
+      <c r="E7" t="str">
+        <v>home_school,crisis</v>
+      </c>
+      <c r="F7" t="str">
+        <v>危机协同能力不足：危机时情绪失控、指责推诿，拒绝配合处置或撒手不管，危机后无复盘、问题周期性重演，存在升级为 R 类红线（5级）的风险。</v>
+      </c>
+      <c r="G7" t="str">
+        <v>危机时情绪化指责或推诿；拒绝配合处置；危机后不参与复盘、预防措施不落地</v>
+      </c>
+      <c r="H7" t="str">
+        <v>未提前约定危机联络人与应急响应流程；家长对学校处置缺乏信任，危机中先对抗再沟通</v>
+      </c>
+      <c r="I7" t="str">
+        <v>提前与家长约定危机联络人与应急响应流程；危机中先共情、给确定性再谈事实与方案；事后共同复盘并沉淀预防措施</v>
+      </c>
+      <c r="J7" t="str">
+        <v>家校沟通与合作test0730-AI入口（评估量表V2.0/归因库/干预方案库/关联关系表）</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J7"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -714,22 +723,22 @@
         <v>HS_EV_01</v>
       </c>
       <c r="B2" t="str">
-        <v>HS_AT_CONFLICT</v>
+        <v>HS_AT_01</v>
       </c>
       <c r="C2" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_S1</v>
       </c>
       <c r="D2" t="str">
-        <v>维度[HS_ATTITUDE] &gt;= 4</v>
+        <v>维度[HS_S1D1] &lt;= 3</v>
       </c>
       <c r="E2" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F2" t="str">
-        <v>沟通态度维度处于高位，已出现越界表达</v>
+        <v>沟通质量维度进入风险区间，信息通道不畅</v>
       </c>
       <c r="G2" t="str">
-        <v>家校沟通合作手册v1</v>
+        <v>家校沟通与合作test0730-AI入口（评估量表V2.0/归因库/干预方案库/关联关系表）</v>
       </c>
     </row>
     <row r="3">
@@ -737,22 +746,22 @@
         <v>HS_EV_02</v>
       </c>
       <c r="B3" t="str">
-        <v>HS_AT_CONFLICT</v>
+        <v>HS_AT_01</v>
       </c>
       <c r="C3" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_S1</v>
       </c>
       <c r="D3" t="str">
-        <v>题[att3] &gt;= 4</v>
+        <v>维度[HS_S1D1] &lt;= 2</v>
       </c>
       <c r="E3" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3" t="str">
-        <v>出现威胁、公开抹黑或恶意维权行为</v>
+        <v>沟通质量维度明显偏低，信息通道严重不畅</v>
       </c>
       <c r="G3" t="str">
-        <v>家校沟通合作手册v1</v>
+        <v>家校沟通与合作test0730-AI入口（评估量表V2.0/归因库/干预方案库/关联关系表）</v>
       </c>
     </row>
     <row r="4">
@@ -760,22 +769,22 @@
         <v>HS_EV_03</v>
       </c>
       <c r="B4" t="str">
-        <v>HS_AT_CONFLICT</v>
+        <v>HS_AT_02</v>
       </c>
       <c r="C4" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_S1</v>
       </c>
       <c r="D4" t="str">
-        <v>维度[HS_ATTITUDE] &gt;= 3</v>
+        <v>维度[HS_S1D2] &lt;= 3</v>
       </c>
       <c r="E4" t="str">
         <v>1</v>
       </c>
       <c r="F4" t="str">
-        <v>沟通态度出现值得关注的变化</v>
+        <v>角色边界维度进入风险区间，越界或分工不明</v>
       </c>
       <c r="G4" t="str">
-        <v>家校沟通合作手册v1</v>
+        <v>家校沟通与合作test0730-AI入口（评估量表V2.0/归因库/干预方案库/关联关系表）</v>
       </c>
     </row>
     <row r="5">
@@ -783,22 +792,22 @@
         <v>HS_EV_04</v>
       </c>
       <c r="B5" t="str">
-        <v>HS_AT_CONTAINER</v>
+        <v>HS_AT_02</v>
       </c>
       <c r="C5" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_S1</v>
       </c>
       <c r="D5" t="str">
-        <v>维度[HS_CONTAINER] &gt;= 4</v>
+        <v>维度[HS_S1D2] &lt;= 2</v>
       </c>
       <c r="E5" t="str">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="F5" t="str">
-        <v>关系容器无法承受坦诚讨论</v>
+        <v>角色边界维度明显偏低，越界持续或角色错乱</v>
       </c>
       <c r="G5" t="str">
-        <v>家校沟通合作手册v1</v>
+        <v>家校沟通与合作test0730-AI入口（评估量表V2.0/归因库/干预方案库/关联关系表）</v>
       </c>
     </row>
     <row r="6">
@@ -806,22 +815,22 @@
         <v>HS_EV_05</v>
       </c>
       <c r="B6" t="str">
-        <v>HS_AT_CONTAINER</v>
+        <v>HS_AT_03</v>
       </c>
       <c r="C6" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_S1</v>
       </c>
       <c r="D6" t="str">
-        <v>维度[HS_CONTAINER] &gt;= 3</v>
+        <v>维度[HS_S1D3] &lt;= 3</v>
       </c>
       <c r="E6" t="str">
         <v>1</v>
       </c>
       <c r="F6" t="str">
-        <v>关系容器承载力下降</v>
+        <v>教育一致性维度进入风险区间，理念或规则出现冲突</v>
       </c>
       <c r="G6" t="str">
-        <v>家校沟通合作手册v1</v>
+        <v>家校沟通与合作test0730-AI入口（评估量表V2.0/归因库/干预方案库/关联关系表）</v>
       </c>
     </row>
     <row r="7">
@@ -829,22 +838,22 @@
         <v>HS_EV_06</v>
       </c>
       <c r="B7" t="str">
-        <v>HS_AT_COOP</v>
+        <v>HS_AT_03</v>
       </c>
       <c r="C7" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_S1</v>
       </c>
       <c r="D7" t="str">
-        <v>维度[HS_COOP] &gt;= 4</v>
+        <v>维度[HS_S1D3] &lt;= 2</v>
       </c>
       <c r="E7" t="str">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="F7" t="str">
-        <v>配合度维度处于高位，共同行动难以落实</v>
+        <v>教育一致性维度明显偏低，理念深层冲突或公开否定</v>
       </c>
       <c r="G7" t="str">
-        <v>家校沟通合作手册v1</v>
+        <v>家校沟通与合作test0730-AI入口（评估量表V2.0/归因库/干预方案库/关联关系表）</v>
       </c>
     </row>
     <row r="8">
@@ -852,137 +861,137 @@
         <v>HS_EV_07</v>
       </c>
       <c r="B8" t="str">
-        <v>HS_AT_COOP</v>
+        <v>HS_AT_04</v>
       </c>
       <c r="C8" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_S1</v>
       </c>
       <c r="D8" t="str">
-        <v>维度[HS_COOP] &gt;= 3</v>
+        <v>维度[HS_S1D4] &lt;= 3</v>
       </c>
       <c r="E8" t="str">
         <v>1</v>
       </c>
       <c r="F8" t="str">
-        <v>配合度出现下降</v>
+        <v>信任关系维度进入风险区间，信任开始动摇</v>
       </c>
       <c r="G8" t="str">
-        <v>家校沟通合作手册v1</v>
+        <v>家校沟通与合作test0730-AI入口（评估量表V2.0/归因库/干预方案库/关联关系表）</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>HS_EV_21</v>
+        <v>HS_EV_08</v>
       </c>
       <c r="B9" t="str">
-        <v>HS_AT_ANXIETY</v>
+        <v>HS_AT_04</v>
       </c>
       <c r="C9" t="str">
-        <v>HS_PARENT_TYPE</v>
+        <v>HS_S1</v>
       </c>
       <c r="D9" t="str">
-        <v>维度[HS_ANXIETY] &gt;= 3.5</v>
+        <v>维度[HS_S1D4] &lt;= 2</v>
       </c>
       <c r="E9" t="str">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="F9" t="str">
-        <v>家长焦虑水平偏高，难以处理复杂信息</v>
+        <v>信任关系维度明显偏低，信任崩塌、预设恶意</v>
       </c>
       <c r="G9" t="str">
-        <v>家校沟通合作手册v1</v>
+        <v>家校沟通与合作test0730-AI入口（评估量表V2.0/归因库/干预方案库/关联关系表）</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>HS_EV_22</v>
+        <v>HS_EV_09</v>
       </c>
       <c r="B10" t="str">
-        <v>HS_AT_ANXIETY</v>
+        <v>HS_AT_05</v>
       </c>
       <c r="C10" t="str">
-        <v>HS_PARENT_TYPE</v>
+        <v>HS_S1</v>
       </c>
       <c r="D10" t="str">
-        <v>维度[HS_ANXIETY] &gt;= 3</v>
+        <v>维度[HS_S1D5] &lt;= 3</v>
       </c>
       <c r="E10" t="str">
         <v>1</v>
       </c>
       <c r="F10" t="str">
-        <v>家长出现焦虑信号</v>
+        <v>参与效能维度进入风险区间，共同行动难以落实</v>
       </c>
       <c r="G10" t="str">
-        <v>家校沟通合作手册v1</v>
+        <v>家校沟通与合作test0730-AI入口（评估量表V2.0/归因库/干预方案库/关联关系表）</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>HS_EV_23</v>
+        <v>HS_EV_10</v>
       </c>
       <c r="B11" t="str">
-        <v>HS_AT_TRUST</v>
+        <v>HS_AT_05</v>
       </c>
       <c r="C11" t="str">
-        <v>HS_PARENT_TYPE</v>
+        <v>HS_S1</v>
       </c>
       <c r="D11" t="str">
-        <v>维度[HS_TRUST] &gt;= 3.5</v>
+        <v>维度[HS_S1D5] &lt;= 2</v>
       </c>
       <c r="E11" t="str">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="F11" t="str">
-        <v>信任基础薄弱，建议先做信任修复</v>
+        <v>参与效能维度明显偏低，参与产生负效应</v>
       </c>
       <c r="G11" t="str">
-        <v>家校沟通合作手册v1</v>
+        <v>家校沟通与合作test0730-AI入口（评估量表V2.0/归因库/干预方案库/关联关系表）</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>HS_EV_24</v>
+        <v>HS_EV_11</v>
       </c>
       <c r="B12" t="str">
-        <v>HS_AT_CONFLICT</v>
+        <v>HS_AT_06</v>
       </c>
       <c r="C12" t="str">
-        <v>HS_PARENT_TYPE</v>
+        <v>HS_S1</v>
       </c>
       <c r="D12" t="str">
-        <v>维度[HS_CONTROL] &gt;= 4</v>
+        <v>维度[HS_S1D6] &lt;= 3</v>
       </c>
       <c r="E12" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12" t="str">
-        <v>控制倾向强且质疑较多，存在冲突升级风险</v>
+        <v>危机响应维度进入风险区间，危机协同能力不足</v>
       </c>
       <c r="G12" t="str">
-        <v>家校沟通合作手册v1</v>
+        <v>家校沟通与合作test0730-AI入口（评估量表V2.0/归因库/干预方案库/关联关系表）</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>HS_EV_25</v>
+        <v>HS_EV_12</v>
       </c>
       <c r="B13" t="str">
-        <v>HS_AT_TRUST</v>
+        <v>HS_AT_06</v>
       </c>
       <c r="C13" t="str">
-        <v>HS_PARENT_TYPE</v>
+        <v>HS_S1</v>
       </c>
       <c r="D13" t="str">
-        <v>维度[HS_TRUST] &gt;= 3</v>
+        <v>维度[HS_S1D6] &lt;= 2</v>
       </c>
       <c r="E13" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" t="str">
-        <v>信任基础需要巩固</v>
+        <v>危机响应维度明显偏低，危机中对抗或推诿、存在升级红线风险</v>
       </c>
       <c r="G13" t="str">
-        <v>家校沟通合作手册v1</v>
+        <v>家校沟通与合作test0730-AI入口（评估量表V2.0/归因库/干预方案库/关联关系表）</v>
       </c>
     </row>
   </sheetData>
@@ -994,7 +1003,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:P7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1048,25 +1057,25 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>HS_GRADE_E</v>
+        <v>HS_GR_01</v>
       </c>
       <c r="B2" t="str">
         <v>home_school</v>
       </c>
       <c r="C2" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_S2</v>
       </c>
       <c r="D2" t="str">
         <v>10</v>
       </c>
       <c r="E2" t="str">
-        <v>题[att3] &gt;= 4</v>
+        <v>题[q1] &gt;= 1 或 题[q2] &gt;= 1 或 题[q3] &gt;= 1 或 题[q4] &gt;= 1 或 题[q5] &gt;= 1 或 题[q6] &gt;= 1 或 题[q7] &gt;= 1 或 题[q8] &gt;= 1</v>
       </c>
       <c r="F2" t="str">
-        <v>E</v>
+        <v>red</v>
       </c>
       <c r="G2" t="str">
-        <v>E 级保护通道</v>
+        <v>5级·极重（危机干预）</v>
       </c>
       <c r="H2" t="str">
         <v>crisis</v>
@@ -1075,48 +1084,48 @@
         <v>是</v>
       </c>
       <c r="J2" t="str">
-        <v>出现威胁或恶意维权行为，已转入保护通道，请勿单独沟通。</v>
+        <v>R 类红线命中，已熔断转五级危机干预：保护安全优先，控制损害，班主任不单独应对。</v>
       </c>
       <c r="K2" t="str">
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>年级组长/校方</v>
+        <v>校长/分管校长（全系统应急响应）</v>
       </c>
       <c r="M2" t="str">
         <v/>
       </c>
       <c r="N2" t="str">
-        <v/>
+        <v>HS_RX_07</v>
       </c>
       <c r="O2" t="str">
-        <v/>
+        <v>停止教师单独沟通，班主任只做信息汇总；保护学生与教师安全，控制信息传播；全程留痕，必要时联系法律顾问或警方</v>
       </c>
       <c r="P2" t="str">
-        <v>家校沟通合作手册v1</v>
+        <v>家校沟通与合作test0730-AI入口（评估量表V2.0/归因库/干预方案库/关联关系表）</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>HS_GRADE_D</v>
+        <v>HS_GR_02</v>
       </c>
       <c r="B3" t="str">
         <v>home_school</v>
       </c>
       <c r="C3" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_S1</v>
       </c>
       <c r="D3" t="str">
         <v>20</v>
       </c>
       <c r="E3" t="str">
-        <v>风险总分 &gt;= 32</v>
+        <v>维度[HS_S1D1] &lt;= 2 或 维度[HS_S1D2] &lt;= 2 或 维度[HS_S1D3] &lt;= 2 或 维度[HS_S1D4] &lt;= 2 或 维度[HS_S1D5] &lt;= 2 或 维度[HS_S1D6] &lt;= 2 或 均分 &lt;= 2.5</v>
       </c>
       <c r="F3" t="str">
-        <v>D</v>
+        <v>orange</v>
       </c>
       <c r="G3" t="str">
-        <v>D 级高冲突</v>
+        <v>4级·重度（强化干预）</v>
       </c>
       <c r="H3" t="str">
         <v>high</v>
@@ -1125,166 +1134,166 @@
         <v>否</v>
       </c>
       <c r="J3" t="str">
-        <v>沟通风险较高，建议由年级组长陪同沟通并全程留痕。</v>
+        <v>多维度进入重度风险（4级），强化干预组接管：班主任不再单独应对，多方协作全程留痕。</v>
       </c>
       <c r="K3" t="str">
-        <v>连续两次 D 级</v>
+        <v>出现 R 类红线或连续两次 4 级</v>
       </c>
       <c r="L3" t="str">
-        <v>年级组长</v>
+        <v>德育主任/管理层</v>
       </c>
       <c r="M3" t="str">
-        <v>7天后复评</v>
+        <v>2周后六维复评</v>
       </c>
       <c r="N3" t="str">
-        <v/>
+        <v>HS_RX_03;HS_RX_02</v>
       </c>
       <c r="O3" t="str">
-        <v/>
+        <v>组建强化干预组（心理团队+德育主任+管理层），班主任不再单独面对家长；每周一次多方协作会，产出家校关系诊断报告；全程留痕，班主任容器状态每周评估</v>
       </c>
       <c r="P3" t="str">
-        <v>家校沟通合作手册v1</v>
+        <v>家校沟通与合作test0730-AI入口（评估量表V2.0/归因库/干预方案库/关联关系表）</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>HS_GRADE_C</v>
+        <v>HS_GR_03</v>
       </c>
       <c r="B4" t="str">
         <v>home_school</v>
       </c>
       <c r="C4" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_S1</v>
       </c>
       <c r="D4" t="str">
         <v>30</v>
       </c>
       <c r="E4" t="str">
-        <v>风险总分 &gt;= 25</v>
+        <v>维度[HS_S1D1] &lt;= 3 或 维度[HS_S1D2] &lt;= 3 或 维度[HS_S1D3] &lt;= 3 或 维度[HS_S1D4] &lt;= 3 或 维度[HS_S1D5] &lt;= 3 或 维度[HS_S1D6] &lt;= 3 或 均分 &lt;= 3</v>
       </c>
       <c r="F4" t="str">
-        <v>C</v>
+        <v>yellow</v>
       </c>
       <c r="G4" t="str">
-        <v>C 级需谨慎</v>
+        <v>3级·中度（定向干预）</v>
       </c>
       <c r="H4" t="str">
-        <v>high</v>
+        <v>medium</v>
       </c>
       <c r="I4" t="str">
         <v>否</v>
       </c>
       <c r="J4" t="str">
-        <v>沟通存在明显阻力，建议先稳住情绪和事实边界，再决定沟通节奏。</v>
+        <v>多维度进入中度风险（3级），心理教师+班主任+年级组长三方协同定向干预。</v>
       </c>
       <c r="K4" t="str">
-        <v>连续两次 C 级</v>
+        <v>连续两次 3 级或出现 O 类叠加</v>
       </c>
       <c r="L4" t="str">
-        <v>年级组长</v>
+        <v>心理教师/年级组长</v>
       </c>
       <c r="M4" t="str">
-        <v>14天后复评</v>
+        <v>2周后六维复评</v>
       </c>
       <c r="N4" t="str">
-        <v/>
+        <v>HS_RX_01;HS_RX_05</v>
       </c>
       <c r="O4" t="str">
-        <v/>
+        <v>心理教师主导 BPS 归因并评估容器状态，班主任提供日常观察数据；由年级组长陪同完成一次家校沟通并记录沟通纪要；每周固定反馈节奏，稳定信息通道</v>
       </c>
       <c r="P4" t="str">
-        <v>家校沟通合作手册v1</v>
+        <v>家校沟通与合作test0730-AI入口（评估量表V2.0/归因库/干预方案库/关联关系表）</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>HS_GRADE_B</v>
+        <v>HS_GR_04</v>
       </c>
       <c r="B5" t="str">
         <v>home_school</v>
       </c>
       <c r="C5" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_S1</v>
       </c>
       <c r="D5" t="str">
         <v>40</v>
       </c>
       <c r="E5" t="str">
-        <v>风险总分 &gt;= 18</v>
+        <v>维度[HS_S1D1] &lt;= 4 或 维度[HS_S1D2] &lt;= 4 或 维度[HS_S1D3] &lt;= 4 或 维度[HS_S1D4] &lt;= 4 或 维度[HS_S1D5] &lt;= 4 或 维度[HS_S1D6] &lt;= 4 或 均分 &lt;= 3.6</v>
       </c>
       <c r="F5" t="str">
-        <v>B</v>
+        <v>blue</v>
       </c>
       <c r="G5" t="str">
-        <v>B 级需铺垫</v>
+        <v>2级·轻度（普及干预）</v>
       </c>
       <c r="H5" t="str">
-        <v>medium</v>
+        <v>low</v>
       </c>
       <c r="I5" t="str">
         <v>否</v>
       </c>
       <c r="J5" t="str">
-        <v>沟通前需要做一定铺垫，重点是先修复关系容器。</v>
+        <v>家校关系出现轻度磨损（2级），班主任主导+年级组长支持，针对性沟通调整策略。</v>
       </c>
       <c r="K5" t="str">
-        <v>复评升级到 C 级或以上</v>
+        <v>连续两次 2 级或出现 O 类触发</v>
       </c>
       <c r="L5" t="str">
         <v>年级组长</v>
       </c>
       <c r="M5" t="str">
-        <v>30天后复评</v>
+        <v>4周后六维复评</v>
       </c>
       <c r="N5" t="str">
-        <v/>
+        <v>HS_RX_04;HS_RX_06</v>
       </c>
       <c r="O5" t="str">
-        <v/>
+        <v>明确家校分工并签署三方协议，年级组长见证；两周内完成一次针对性沟通，修补信任小缺口；建立每周反馈节奏，跟进约定履行情况</v>
       </c>
       <c r="P5" t="str">
-        <v>家校沟通合作手册v1</v>
+        <v>家校沟通与合作test0730-AI入口（评估量表V2.0/归因库/干预方案库/关联关系表）</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>HS_GRADE_TYPE_D</v>
+        <v>HS_GR_05</v>
       </c>
       <c r="B6" t="str">
         <v>home_school</v>
       </c>
       <c r="C6" t="str">
-        <v>HS_PARENT_TYPE</v>
+        <v>HS_S2</v>
       </c>
       <c r="D6" t="str">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="E6" t="str">
-        <v>均分 &gt;= 4</v>
+        <v>题[q1] &lt;= 0 且 题[q2] &lt;= 0 且 题[q3] &lt;= 0 且 题[q4] &lt;= 0 且 题[q5] &lt;= 0 且 题[q6] &lt;= 0 且 题[q7] &lt;= 0 且 题[q8] &lt;= 0</v>
       </c>
       <c r="F6" t="str">
-        <v>D</v>
+        <v>green</v>
       </c>
       <c r="G6" t="str">
-        <v>D 级高冲突</v>
+        <v>红线检查通过</v>
       </c>
       <c r="H6" t="str">
-        <v>high</v>
+        <v>low</v>
       </c>
       <c r="I6" t="str">
         <v>否</v>
       </c>
       <c r="J6" t="str">
-        <v>家长分型显示焦虑或控制倾向偏高、信任基础薄弱，建议由年级组长陪同沟通。</v>
+        <v>R1-R8 红线全部未命中，未触发危机熔断。</v>
       </c>
       <c r="K6" t="str">
-        <v>连续两次 D 级</v>
+        <v>任一 R 类红线命中</v>
       </c>
       <c r="L6" t="str">
-        <v>年级组长</v>
+        <v>危机响应组（全系统应急）</v>
       </c>
       <c r="M6" t="str">
-        <v>7天后复评</v>
+        <v>出现红线信号时立即复评</v>
       </c>
       <c r="N6" t="str">
         <v/>
@@ -1293,48 +1302,48 @@
         <v/>
       </c>
       <c r="P6" t="str">
-        <v>家校沟通合作手册v1</v>
+        <v>家校沟通与合作test0730-AI入口（评估量表V2.0/归因库/干预方案库/关联关系表）</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>HS_GRADE_TYPE_C</v>
+        <v>HS_GR_DEFAULT</v>
       </c>
       <c r="B7" t="str">
         <v>home_school</v>
       </c>
       <c r="C7" t="str">
-        <v>HS_PARENT_TYPE</v>
+        <v/>
       </c>
       <c r="D7" t="str">
-        <v>25</v>
+        <v>999</v>
       </c>
       <c r="E7" t="str">
-        <v>均分 &gt;= 3</v>
+        <v/>
       </c>
       <c r="F7" t="str">
-        <v>C</v>
+        <v>green</v>
       </c>
       <c r="G7" t="str">
-        <v>C 级需谨慎</v>
+        <v>1级·关注（基础预防）</v>
       </c>
       <c r="H7" t="str">
-        <v>high</v>
+        <v>low</v>
       </c>
       <c r="I7" t="str">
         <v>否</v>
       </c>
       <c r="J7" t="str">
-        <v>家长分型提示沟通存在明显阻力，先稳住情绪和事实边界再决定节奏。</v>
+        <v>本次评估未发现需要重点干预的信号</v>
       </c>
       <c r="K7" t="str">
-        <v>连续两次 C 级</v>
+        <v/>
       </c>
       <c r="L7" t="str">
-        <v>年级组长</v>
+        <v/>
       </c>
       <c r="M7" t="str">
-        <v>14天后复评</v>
+        <v/>
       </c>
       <c r="N7" t="str">
         <v/>
@@ -1343,112 +1352,12 @@
         <v/>
       </c>
       <c r="P7" t="str">
-        <v>家校沟通合作手册v1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>HS_GRADE_TYPE_B</v>
-      </c>
-      <c r="B8" t="str">
-        <v>home_school</v>
-      </c>
-      <c r="C8" t="str">
-        <v>HS_PARENT_TYPE</v>
-      </c>
-      <c r="D8" t="str">
-        <v>35</v>
-      </c>
-      <c r="E8" t="str">
-        <v>均分 &gt;= 2</v>
-      </c>
-      <c r="F8" t="str">
-        <v>B</v>
-      </c>
-      <c r="G8" t="str">
-        <v>B 级需铺垫</v>
-      </c>
-      <c r="H8" t="str">
-        <v>medium</v>
-      </c>
-      <c r="I8" t="str">
-        <v>否</v>
-      </c>
-      <c r="J8" t="str">
-        <v>家长分型提示沟通前需要一定铺垫，重点是先修复关系容器。</v>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v/>
-      </c>
-      <c r="M8" t="str">
-        <v/>
-      </c>
-      <c r="N8" t="str">
-        <v/>
-      </c>
-      <c r="O8" t="str">
-        <v/>
-      </c>
-      <c r="P8" t="str">
-        <v>家校沟通合作手册v1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>HS_GRADE_A</v>
-      </c>
-      <c r="B9" t="str">
-        <v>home_school</v>
-      </c>
-      <c r="C9" t="str">
-        <v/>
-      </c>
-      <c r="D9" t="str">
-        <v>999</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v>A</v>
-      </c>
-      <c r="G9" t="str">
-        <v>A 级常规沟通</v>
-      </c>
-      <c r="H9" t="str">
-        <v>low</v>
-      </c>
-      <c r="I9" t="str">
-        <v>否</v>
-      </c>
-      <c r="J9" t="str">
-        <v>家校关系状况良好，可按常规节奏沟通。</v>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v/>
-      </c>
-      <c r="M9" t="str">
-        <v/>
-      </c>
-      <c r="N9" t="str">
-        <v/>
-      </c>
-      <c r="O9" t="str">
-        <v/>
-      </c>
-      <c r="P9" t="str">
-        <v>家校沟通合作手册v1</v>
+        <v>家校沟通与合作test0730-AI入口（评估量表V2.0/归因库/干预方案库/关联关系表）</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P7"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1494,31 +1403,31 @@
         <v>home_school</v>
       </c>
       <c r="B2" t="str">
-        <v>题[att3] &gt;= 5</v>
+        <v>量表[HS_S2].题[q1] &gt;= 1 或 量表[HS_S2].题[q2] &gt;= 1 或 量表[HS_S2].题[q3] &gt;= 1 或 量表[HS_S2].题[q4] &gt;= 1 或 量表[HS_S2].题[q5] &gt;= 1 或 量表[HS_S2].题[q6] &gt;= 1 或 量表[HS_S2].题[q7] &gt;= 1 或 量表[HS_S2].题[q8] &gt;= 1</v>
       </c>
       <c r="C2" t="str">
-        <v>家长出现明确威胁、公开抹黑或恶意维权行为</v>
+        <v>R 类红线命中，已熔断转五级危机干预：保护安全优先，控制损害，班主任不单独应对。</v>
       </c>
       <c r="D2" t="str">
         <v>module</v>
       </c>
       <c r="E2" t="str">
-        <v>停止教师单独沟通，转入学校保护通道，全程留痕并由年级组长或校方介入</v>
+        <v>班主任不再单独面对家长，只做信息汇总；保护学生与教师安全，控制信息传播；必要时联系法律顾问或警方</v>
       </c>
       <c r="F2" t="str">
-        <v>停止单独沟通,启用保护通道,全程留痕,通知年级组长,必要时上报校方</v>
+        <v>停止单独沟通；启用保护通道；全程留痕；通知年级组长；必要时上报校方</v>
       </c>
       <c r="G2" t="str">
-        <v>经年级组长评估确认沟通可恢复常规</v>
+        <v>经学校危机响应组评估确认风险解除后</v>
       </c>
       <c r="H2" t="str">
-        <v>年级组长</v>
+        <v>德育主任</v>
       </c>
       <c r="I2" t="str">
-        <v>[班级]家校沟通触发 E 级保护通道，请勿让班主任单独沟通。</v>
+        <v>[班级]家校沟通触发 5 级危机干预（R 类红线命中），班主任停止单独沟通，启动全系统应急响应。</v>
       </c>
       <c r="J2" t="str">
-        <v>家校沟通合作手册v1</v>
+        <v>家校沟通与合作test0730-AI入口（评估量表V2.0/归因库/干预方案库/关联关系表）</v>
       </c>
     </row>
   </sheetData>
